--- a/data/equipments/equipment_data.xlsx
+++ b/data/equipments/equipment_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\IRIS_docs\data\equipments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IRIS_docs\data\equipments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D87E3319-DB7B-42AD-9985-815A57562C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E7AD4F-BA88-4D4D-B37B-AC09BA38227B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="192" windowWidth="38916" windowHeight="16488" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="55">
   <si>
     <t>id</t>
   </si>
@@ -97,28 +97,94 @@
     <t>[0, 0]</t>
   </si>
   <si>
-    <t>Нефтегазосборный трубопровод от блока замера жидкости БГЗЖ куста скважин К-524/3 до УП-10/4</t>
-  </si>
-  <si>
-    <t>Система промысловых трубопроводов Кузайкинского месторождения нефти</t>
-  </si>
-  <si>
-    <t>Нефтегазосборный трубопровод от блока замера жидкости БГЗЖ куста скважин К-526/2 до УП-13/3</t>
-  </si>
-  <si>
-    <t>Нефтегазосборный трубопровод от блока замера жидкости БГЗЖ куста скважин К-15186/2 до УП-8</t>
-  </si>
-  <si>
-    <t>Технологические трубопроводы куста скважин К-526/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Технологические трубопроводы куста скважин К-524/3 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Технологические трубопроводы куста скважин К-15186/2 </t>
-  </si>
-  <si>
-    <t>Технологические трубопроводы куста скважин К-15186</t>
+    <t>Сепаратор С-1</t>
+  </si>
+  <si>
+    <t>ж.ф.+г.ф.</t>
+  </si>
+  <si>
+    <t>Отстойник нефти О-1/1-3</t>
+  </si>
+  <si>
+    <t>Электродегидратор ЭГ-1/1-2</t>
+  </si>
+  <si>
+    <t>Буферная емкость Е-1</t>
+  </si>
+  <si>
+    <t>Маслоотделитель М-1/1-3</t>
+  </si>
+  <si>
+    <t>Сепаратор газа С-7/1-3</t>
+  </si>
+  <si>
+    <t>Сепаратор концевой С-4/1-6</t>
+  </si>
+  <si>
+    <t>Пункт подготовки и сбора нефти</t>
+  </si>
+  <si>
+    <t>Отстойник нефти О-1,2</t>
+  </si>
+  <si>
+    <t>Резервуар пластовой воды РВС-18,20,52</t>
+  </si>
+  <si>
+    <t>Емкость нефти Е-2/2</t>
+  </si>
+  <si>
+    <t>Технологические газопроводы</t>
+  </si>
+  <si>
+    <t>г.ф.</t>
+  </si>
+  <si>
+    <t>Насосная установка ЦНС</t>
+  </si>
+  <si>
+    <t>Емкость Е-16/3,4</t>
+  </si>
+  <si>
+    <t>Технологический трубопроводы</t>
+  </si>
+  <si>
+    <t>Ёмкость хранения масла T-19</t>
+  </si>
+  <si>
+    <t>Газокомпрессорная</t>
+  </si>
+  <si>
+    <t>Компрессорная установка</t>
+  </si>
+  <si>
+    <t>Емкость хранения метанола Е-1-5</t>
+  </si>
+  <si>
+    <t>Склад метанола</t>
+  </si>
+  <si>
+    <t>Технологические газопроводы (внутренние)</t>
+  </si>
+  <si>
+    <t>Котельная</t>
+  </si>
+  <si>
+    <t>Технологические газопроводы (наружные)</t>
+  </si>
+  <si>
+    <t>Резервуар нефти РВС-5</t>
+  </si>
+  <si>
+    <t>Товарно-сырьевой склад</t>
+  </si>
+  <si>
+    <t>Резервуар нефти РВС-7,8,48</t>
+  </si>
+  <si>
+    <t>Резервуар нефти РВС-9</t>
+  </si>
+  <si>
+    <t>Резервуар нефти РВС-47</t>
   </si>
 </sst>
 </file>
@@ -177,8 +243,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FD86AEF1-A835-43E7-8E63-C1CEC91726C0}" name="Таблица2" displayName="Таблица2" ref="A1:W1048563" totalsRowShown="0">
-  <autoFilter ref="A1:W1048563" xr:uid="{FD86AEF1-A835-43E7-8E63-C1CEC91726C0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FD86AEF1-A835-43E7-8E63-C1CEC91726C0}" name="Таблица2" displayName="Таблица2" ref="A1:W1048576" totalsRowShown="0">
+  <autoFilter ref="A1:W1048576" xr:uid="{FD86AEF1-A835-43E7-8E63-C1CEC91726C0}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{F8505ABD-79CE-4B6A-9D66-BB9AD7197A79}" name="id"/>
     <tableColumn id="2" xr3:uid="{FEC89AEE-6880-4DC1-8494-FD1203EEA743}" name="substance_id"/>
@@ -493,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W12"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.33203125" customWidth="1"/>
@@ -593,282 +659,282 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
         <v>25</v>
       </c>
       <c r="D2">
-        <v>128</v>
+        <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="s">
         <v>24</v>
       </c>
       <c r="I2">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="J2">
         <v>89</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="N2">
         <v>1</v>
       </c>
       <c r="O2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="Q2">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="R2">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="S2">
         <v>3600</v>
       </c>
       <c r="T2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="U2">
+        <v>2</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
         <v>26</v>
       </c>
-      <c r="U2">
-        <v>4</v>
-      </c>
-      <c r="V2">
-        <v>1</v>
-      </c>
-      <c r="W2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3">
-        <v>271</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="s">
         <v>24</v>
       </c>
       <c r="I3">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="J3">
         <v>89</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="O3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="Q3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="R3">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="S3">
         <v>3600</v>
       </c>
       <c r="T3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="U3">
+        <v>2</v>
+      </c>
+      <c r="V3">
+        <v>3</v>
+      </c>
+      <c r="W3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
         <v>26</v>
       </c>
-      <c r="U3">
-        <v>4</v>
-      </c>
-      <c r="V3">
-        <v>1</v>
-      </c>
-      <c r="W3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4">
-        <v>1223</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="s">
         <v>24</v>
       </c>
       <c r="I4">
-        <v>1223</v>
+        <v>100</v>
       </c>
       <c r="J4">
         <v>89</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="O4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Q4">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="R4">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="S4">
         <v>3600</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="U4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="s">
         <v>24</v>
       </c>
       <c r="I5">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J5">
         <v>89</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="N5">
         <v>1</v>
       </c>
       <c r="O5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="R5">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="S5">
         <v>3600</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="U5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V5">
         <v>1</v>
@@ -877,18 +943,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
       </c>
       <c r="D6">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="E6" t="s">
         <v>23</v>
@@ -897,201 +963,1337 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="s">
         <v>24</v>
       </c>
       <c r="I6">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J6">
         <v>89</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="O6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="S6">
         <v>3600</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="U6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
         <v>31</v>
       </c>
       <c r="D7">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="s">
         <v>24</v>
       </c>
       <c r="I7">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="J7">
         <v>89</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="O7">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q7">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="R7">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="S7">
         <v>3600</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="U7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
         <v>32</v>
       </c>
       <c r="D8">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="s">
         <v>24</v>
       </c>
       <c r="I8">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="J8">
         <v>89</v>
       </c>
       <c r="K8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="O8">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Q8">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="R8">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="S8">
         <v>3600</v>
       </c>
       <c r="T8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="U8">
+        <v>2</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
         <v>26</v>
       </c>
-      <c r="U8">
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9">
+        <v>30</v>
+      </c>
+      <c r="J9">
+        <v>89</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>70</v>
+      </c>
+      <c r="M9">
+        <v>0.85</v>
+      </c>
+      <c r="N9">
+        <v>0.6</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>520</v>
+      </c>
+      <c r="Q9">
+        <v>50</v>
+      </c>
+      <c r="R9">
+        <v>100</v>
+      </c>
+      <c r="S9">
+        <v>3600</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="U9">
+        <v>2</v>
+      </c>
+      <c r="V9">
+        <v>2</v>
+      </c>
+      <c r="W9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10">
+        <v>300</v>
+      </c>
+      <c r="J10">
+        <v>159</v>
+      </c>
+      <c r="K10">
+        <v>3</v>
+      </c>
+      <c r="L10">
+        <v>120</v>
+      </c>
+      <c r="M10">
+        <v>0.95</v>
+      </c>
+      <c r="N10">
+        <v>0.1</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>1600</v>
+      </c>
+      <c r="Q10">
+        <v>10</v>
+      </c>
+      <c r="R10">
+        <v>100</v>
+      </c>
+      <c r="S10">
+        <v>3600</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="U10">
+        <v>3</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11">
+        <v>60</v>
+      </c>
+      <c r="J11">
+        <v>89</v>
+      </c>
+      <c r="K11">
+        <v>3</v>
+      </c>
+      <c r="L11">
+        <v>10</v>
+      </c>
+      <c r="M11">
+        <v>0.85</v>
+      </c>
+      <c r="N11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>250</v>
+      </c>
+      <c r="Q11">
+        <v>50</v>
+      </c>
+      <c r="R11">
+        <v>100</v>
+      </c>
+      <c r="S11">
+        <v>3600</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="U11">
+        <v>2</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12">
+        <v>55</v>
+      </c>
+      <c r="J12">
+        <v>100</v>
+      </c>
+      <c r="K12">
+        <v>3</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>10</v>
+      </c>
+      <c r="R12">
+        <v>100</v>
+      </c>
+      <c r="S12">
+        <v>3600</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="U12">
+        <v>2</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+      <c r="W12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13">
+        <v>27</v>
+      </c>
+      <c r="E13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
         <v>4</v>
       </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="T12" s="1"/>
+      <c r="H13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13">
+        <v>50</v>
+      </c>
+      <c r="J13">
+        <v>100</v>
+      </c>
+      <c r="K13">
+        <v>3</v>
+      </c>
+      <c r="L13">
+        <v>0.2</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>60</v>
+      </c>
+      <c r="Q13">
+        <v>50</v>
+      </c>
+      <c r="R13">
+        <v>100</v>
+      </c>
+      <c r="S13">
+        <v>3600</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="U13">
+        <v>2</v>
+      </c>
+      <c r="V13">
+        <v>1</v>
+      </c>
+      <c r="W13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14">
+        <v>30</v>
+      </c>
+      <c r="J14">
+        <v>159</v>
+      </c>
+      <c r="K14">
+        <v>3</v>
+      </c>
+      <c r="L14">
+        <v>7</v>
+      </c>
+      <c r="M14">
+        <v>0.85</v>
+      </c>
+      <c r="N14">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>130</v>
+      </c>
+      <c r="Q14">
+        <v>10</v>
+      </c>
+      <c r="R14">
+        <v>100</v>
+      </c>
+      <c r="S14">
+        <v>3600</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="U14">
+        <v>2</v>
+      </c>
+      <c r="V14">
+        <v>1</v>
+      </c>
+      <c r="W14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15">
+        <v>58</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15">
+        <v>1233</v>
+      </c>
+      <c r="J15">
+        <v>159</v>
+      </c>
+      <c r="K15">
+        <v>3</v>
+      </c>
+      <c r="L15">
+        <v>5</v>
+      </c>
+      <c r="M15">
+        <v>0.85</v>
+      </c>
+      <c r="N15">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>300</v>
+      </c>
+      <c r="Q15">
+        <v>50</v>
+      </c>
+      <c r="R15">
+        <v>100</v>
+      </c>
+      <c r="S15">
+        <v>3600</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="U15">
+        <v>2</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+      <c r="W15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16">
+        <v>60</v>
+      </c>
+      <c r="J16">
+        <v>89</v>
+      </c>
+      <c r="K16">
+        <v>5</v>
+      </c>
+      <c r="L16">
+        <v>23</v>
+      </c>
+      <c r="M16">
+        <v>0.95</v>
+      </c>
+      <c r="N16">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>80</v>
+      </c>
+      <c r="Q16">
+        <v>10</v>
+      </c>
+      <c r="R16">
+        <v>100</v>
+      </c>
+      <c r="S16">
+        <v>3600</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="U16">
+        <v>2</v>
+      </c>
+      <c r="V16">
+        <v>1</v>
+      </c>
+      <c r="W16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17">
+        <v>550</v>
+      </c>
+      <c r="J17">
+        <v>219</v>
+      </c>
+      <c r="K17">
+        <v>3</v>
+      </c>
+      <c r="L17">
+        <v>0.3</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>10</v>
+      </c>
+      <c r="R17">
+        <v>300</v>
+      </c>
+      <c r="S17">
+        <v>3600</v>
+      </c>
+      <c r="T17" t="s">
+        <v>43</v>
+      </c>
+      <c r="U17">
+        <v>2</v>
+      </c>
+      <c r="V17">
+        <v>2</v>
+      </c>
+      <c r="W17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18">
+        <v>5</v>
+      </c>
+      <c r="E18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18">
+        <v>300</v>
+      </c>
+      <c r="J18">
+        <v>159</v>
+      </c>
+      <c r="K18">
+        <v>3</v>
+      </c>
+      <c r="L18">
+        <v>25</v>
+      </c>
+      <c r="M18">
+        <v>0.95</v>
+      </c>
+      <c r="N18">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>260</v>
+      </c>
+      <c r="Q18">
+        <v>10</v>
+      </c>
+      <c r="R18">
+        <v>100</v>
+      </c>
+      <c r="S18">
+        <v>3600</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U18">
+        <v>3</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>7</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19">
+        <v>89</v>
+      </c>
+      <c r="E19" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19">
+        <v>150</v>
+      </c>
+      <c r="J19">
+        <v>100</v>
+      </c>
+      <c r="K19">
+        <v>3</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>10</v>
+      </c>
+      <c r="R19">
+        <v>300</v>
+      </c>
+      <c r="S19">
+        <v>3600</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="U19">
+        <v>3</v>
+      </c>
+      <c r="V19">
+        <v>2</v>
+      </c>
+      <c r="W19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>7</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20">
+        <v>89</v>
+      </c>
+      <c r="E20" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20">
+        <v>350</v>
+      </c>
+      <c r="J20">
+        <v>100</v>
+      </c>
+      <c r="K20">
+        <v>3</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0.5</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>10</v>
+      </c>
+      <c r="R20">
+        <v>300</v>
+      </c>
+      <c r="S20">
+        <v>3600</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="U20">
+        <v>3</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21">
+        <v>450</v>
+      </c>
+      <c r="J21">
+        <v>159</v>
+      </c>
+      <c r="K21">
+        <v>3</v>
+      </c>
+      <c r="L21">
+        <v>240</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>0.1</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>2500</v>
+      </c>
+      <c r="Q21">
+        <v>10</v>
+      </c>
+      <c r="R21">
+        <v>100</v>
+      </c>
+      <c r="S21">
+        <v>3600</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U21">
+        <v>3</v>
+      </c>
+      <c r="V21">
+        <v>1</v>
+      </c>
+      <c r="W21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22">
+        <v>450</v>
+      </c>
+      <c r="J22">
+        <v>159</v>
+      </c>
+      <c r="K22">
+        <v>3</v>
+      </c>
+      <c r="L22">
+        <v>860</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>0.1</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>3200</v>
+      </c>
+      <c r="Q22">
+        <v>10</v>
+      </c>
+      <c r="R22">
+        <v>100</v>
+      </c>
+      <c r="S22">
+        <v>3600</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U22">
+        <v>3</v>
+      </c>
+      <c r="V22">
+        <v>2</v>
+      </c>
+      <c r="W22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23">
+        <v>450</v>
+      </c>
+      <c r="J23">
+        <v>159</v>
+      </c>
+      <c r="K23">
+        <v>3</v>
+      </c>
+      <c r="L23">
+        <v>3100</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>0.1</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>3700</v>
+      </c>
+      <c r="Q23">
+        <v>10</v>
+      </c>
+      <c r="R23">
+        <v>100</v>
+      </c>
+      <c r="S23">
+        <v>3600</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U23">
+        <v>3</v>
+      </c>
+      <c r="V23">
+        <v>2</v>
+      </c>
+      <c r="W23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24">
+        <v>450</v>
+      </c>
+      <c r="J24">
+        <v>159</v>
+      </c>
+      <c r="K24">
+        <v>3</v>
+      </c>
+      <c r="L24">
+        <v>3850</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>0.1</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>4500</v>
+      </c>
+      <c r="Q24">
+        <v>10</v>
+      </c>
+      <c r="R24">
+        <v>100</v>
+      </c>
+      <c r="S24">
+        <v>3600</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U24">
+        <v>3</v>
+      </c>
+      <c r="V24">
+        <v>3</v>
+      </c>
+      <c r="W24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="T25" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/equipments/equipment_data.xlsx
+++ b/data/equipments/equipment_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IRIS_docs\data\equipments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E7AD4F-BA88-4D4D-B37B-AC09BA38227B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3860881-46EF-40E3-9D87-56D9BD1577AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1602,7 +1602,7 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="s">
         <v>24</v>

--- a/data/equipments/equipment_data.xlsx
+++ b/data/equipments/equipment_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\IRIS_docs\data\equipments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2951181A-E0A2-4399-8C10-D192389D6FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A17C53-4A92-47D6-AECD-309CB1C8CCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="192" windowWidth="38916" windowHeight="16488" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2364" yWindow="192" windowWidth="38916" windowHeight="16488" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
   <si>
     <t>id</t>
   </si>
@@ -97,37 +97,16 @@
     <t>[0, 0]</t>
   </si>
   <si>
-    <t>Напорный трубопровод подземный, стальной. ДНС-Западно-Угутская → уз.27</t>
-  </si>
-  <si>
-    <t>Система межпромысловых трубопроводов Западно-Угутского месторождения</t>
-  </si>
-  <si>
-    <t>Напорный трубопровод подземный, стальной. уз.27 → уз.камеры пуска</t>
-  </si>
-  <si>
-    <t>Напорный трубопровод подземный, стальной. уз.камеры пуска → уз.28 (т.вр.12й км)</t>
-  </si>
-  <si>
-    <t>Напорный трубопровод подземный, стальной. уз.28 → уз.29 (т.вр.31й км)</t>
-  </si>
-  <si>
-    <t>Напорный трубопровод подземный, стальной. уз.29 → т.19Е</t>
-  </si>
-  <si>
-    <t>Напорный трубопровод подземный, стальной. т.19Е → УПСВ-3</t>
-  </si>
-  <si>
-    <t>Напорный трубопровод подземный, стальной. уз.21 → ДНС-Западно-Угутская</t>
-  </si>
-  <si>
-    <t>Напорный трубопровод подземный, стальной. уз.6 → уз.5а</t>
-  </si>
-  <si>
-    <t>Напорный трубопровод подземный, стальной. уз.19 → уз.6</t>
-  </si>
-  <si>
-    <t>Установка дозирования УДПХ-Лозна</t>
+    <t>Система промысловых трубопроводов  Тавельского месторождения  нефти</t>
+  </si>
+  <si>
+    <t>Выкидной нефтегазопровод от скв.куста №54 до до сборного нефтегазопровода, нефть</t>
+  </si>
+  <si>
+    <t>Выкидной нефтегазопровод от скважины №1125 до точки врезки в сущ. выкидной трубопровод от скважины №887, нефть</t>
+  </si>
+  <si>
+    <t>Сборный нефтегазопровод от куста скважин №54 до т.вр. в сущ. нефтегазосборный трубопровод от ГЗУ-20, нефть</t>
   </si>
 </sst>
 </file>
@@ -172,7 +151,11 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -186,12 +169,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FD86AEF1-A835-43E7-8E63-C1CEC91726C0}" name="Таблица2" displayName="Таблица2" ref="A1:W1048563" totalsRowShown="0">
-  <autoFilter ref="A1:W1048563" xr:uid="{FD86AEF1-A835-43E7-8E63-C1CEC91726C0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FD86AEF1-A835-43E7-8E63-C1CEC91726C0}" name="Таблица2" displayName="Таблица2" ref="A1:W1048554" totalsRowShown="0">
+  <autoFilter ref="A1:W1048554" xr:uid="{FD86AEF1-A835-43E7-8E63-C1CEC91726C0}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{F8505ABD-79CE-4B6A-9D66-BB9AD7197A79}" name="id"/>
     <tableColumn id="2" xr3:uid="{FEC89AEE-6880-4DC1-8494-FD1203EEA743}" name="substance_id"/>
-    <tableColumn id="3" xr3:uid="{B811839C-BB37-4B7A-BCA4-151CB7FBE73A}" name="equipment_name"/>
+    <tableColumn id="3" xr3:uid="{B811839C-BB37-4B7A-BCA4-151CB7FBE73A}" name="equipment_name" dataDxfId="0"/>
     <tableColumn id="4" xr3:uid="{6A0467C8-1103-4F62-9172-B7B57D09DECA}" name="quantity_equipment"/>
     <tableColumn id="5" xr3:uid="{FDB96BBF-CE31-4BED-9D81-B6C45F782B33}" name="phase_state"/>
     <tableColumn id="6" xr3:uid="{D4A804DB-EE4B-49B0-9B40-0BDF726E930B}" name="coord_type"/>
@@ -502,12 +485,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W12"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.33203125" customWidth="1"/>
     <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="3" width="33.6640625" customWidth="1"/>
+    <col min="3" max="3" width="33.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="19.21875" customWidth="1"/>
     <col min="5" max="5" width="12.77734375" customWidth="1"/>
     <col min="6" max="6" width="12.21875" customWidth="1"/>
@@ -538,7 +521,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -607,13 +590,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="D2">
-        <v>400</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>23</v>
@@ -628,13 +611,13 @@
         <v>24</v>
       </c>
       <c r="I2">
-        <v>400</v>
+        <v>31</v>
       </c>
       <c r="J2">
-        <v>530</v>
+        <v>89</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -643,7 +626,7 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="O2">
         <v>20</v>
@@ -661,30 +644,30 @@
         <v>3600</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="D3">
-        <v>379</v>
+        <v>332</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
@@ -699,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="I3">
-        <v>379</v>
+        <v>332</v>
       </c>
       <c r="J3">
-        <v>530</v>
+        <v>114</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -714,7 +697,7 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="O3">
         <v>20</v>
@@ -732,30 +715,30 @@
         <v>3600</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V3">
         <v>1</v>
       </c>
       <c r="W3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
       <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="D4">
-        <v>12700</v>
+        <v>738</v>
       </c>
       <c r="E4" t="s">
         <v>23</v>
@@ -770,13 +753,13 @@
         <v>24</v>
       </c>
       <c r="I4">
-        <v>1270</v>
+        <v>738</v>
       </c>
       <c r="J4">
-        <v>530</v>
+        <v>114</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -785,7 +768,7 @@
         <v>1</v>
       </c>
       <c r="N4">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="O4">
         <v>20</v>
@@ -803,585 +786,26 @@
         <v>3600</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5">
-        <v>18400</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5">
-        <v>1840</v>
-      </c>
-      <c r="J5">
-        <v>530</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>2.5</v>
-      </c>
-      <c r="O5">
-        <v>20</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>50</v>
-      </c>
-      <c r="R5">
-        <v>12</v>
-      </c>
-      <c r="S5">
-        <v>3600</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U5">
-        <v>3</v>
-      </c>
-      <c r="V5">
-        <v>1</v>
-      </c>
-      <c r="W5">
-        <v>2</v>
-      </c>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="T5" s="1"/>
     </row>
-    <row r="6" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6">
-        <v>21396</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6">
-        <v>2139</v>
-      </c>
-      <c r="J6">
-        <v>530</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6">
-        <v>2.5</v>
-      </c>
-      <c r="O6">
-        <v>20</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>50</v>
-      </c>
-      <c r="R6">
-        <v>12</v>
-      </c>
-      <c r="S6">
-        <v>3600</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U6">
-        <v>3</v>
-      </c>
-      <c r="V6">
-        <v>1</v>
-      </c>
-      <c r="W6">
-        <v>2</v>
-      </c>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="T6" s="1"/>
     </row>
-    <row r="7" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7">
-        <v>450</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7">
-        <v>450</v>
-      </c>
-      <c r="J7">
-        <v>530</v>
-      </c>
-      <c r="K7">
-        <v>5</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>2.5</v>
-      </c>
-      <c r="O7">
-        <v>20</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>50</v>
-      </c>
-      <c r="R7">
-        <v>12</v>
-      </c>
-      <c r="S7">
-        <v>3600</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U7">
-        <v>3</v>
-      </c>
-      <c r="V7">
-        <v>1</v>
-      </c>
-      <c r="W7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8">
-        <v>745</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8">
-        <v>745</v>
-      </c>
-      <c r="J8">
-        <v>530</v>
-      </c>
-      <c r="K8">
-        <v>5</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>2.5</v>
-      </c>
-      <c r="O8">
-        <v>20</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>50</v>
-      </c>
-      <c r="R8">
-        <v>12</v>
-      </c>
-      <c r="S8">
-        <v>3600</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U8">
-        <v>3</v>
-      </c>
-      <c r="V8">
-        <v>1</v>
-      </c>
-      <c r="W8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9">
-        <v>2227</v>
-      </c>
-      <c r="E9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9">
-        <v>1450</v>
-      </c>
-      <c r="J9">
-        <v>530</v>
-      </c>
-      <c r="K9">
-        <v>5</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="N9">
-        <v>2.5</v>
-      </c>
-      <c r="O9">
-        <v>20</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>50</v>
-      </c>
-      <c r="R9">
-        <v>12</v>
-      </c>
-      <c r="S9">
-        <v>3600</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U9">
-        <v>3</v>
-      </c>
-      <c r="V9">
-        <v>1</v>
-      </c>
-      <c r="W9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10">
-        <v>8915</v>
-      </c>
-      <c r="E10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10">
-        <v>891</v>
-      </c>
-      <c r="J10">
-        <v>530</v>
-      </c>
-      <c r="K10">
-        <v>5</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>1</v>
-      </c>
-      <c r="N10">
-        <v>2.5</v>
-      </c>
-      <c r="O10">
-        <v>20</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>50</v>
-      </c>
-      <c r="R10">
-        <v>12</v>
-      </c>
-      <c r="S10">
-        <v>3600</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U10">
-        <v>3</v>
-      </c>
-      <c r="V10">
-        <v>1</v>
-      </c>
-      <c r="W10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11">
-        <v>8915</v>
-      </c>
-      <c r="E11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11">
-        <v>2569</v>
-      </c>
-      <c r="J11">
-        <v>530</v>
-      </c>
-      <c r="K11">
-        <v>5</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-      <c r="N11">
-        <v>2.5</v>
-      </c>
-      <c r="O11">
-        <v>20</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>50</v>
-      </c>
-      <c r="R11">
-        <v>12</v>
-      </c>
-      <c r="S11">
-        <v>3600</v>
-      </c>
-      <c r="T11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U11">
-        <v>3</v>
-      </c>
-      <c r="V11">
-        <v>2</v>
-      </c>
-      <c r="W11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>6</v>
-      </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-      <c r="N12">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>180</v>
-      </c>
-      <c r="Q12">
-        <v>50</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>3600</v>
-      </c>
-      <c r="T12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U12">
-        <v>3</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>1</v>
-      </c>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="T7" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/equipments/equipment_data.xlsx
+++ b/data/equipments/equipment_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\IRIS_docs\data\equipments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A17C53-4A92-47D6-AECD-309CB1C8CCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC3BB4E-A90B-416C-AC2C-C230E61BDA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2364" yWindow="192" windowWidth="38916" windowHeight="16488" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="192" windowWidth="38916" windowHeight="16488" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="51">
   <si>
     <t>id</t>
   </si>
@@ -97,16 +97,82 @@
     <t>[0, 0]</t>
   </si>
   <si>
-    <t>Система промысловых трубопроводов  Тавельского месторождения  нефти</t>
-  </si>
-  <si>
-    <t>Выкидной нефтегазопровод от скв.куста №54 до до сборного нефтегазопровода, нефть</t>
-  </si>
-  <si>
-    <t>Выкидной нефтегазопровод от скважины №1125 до точки врезки в сущ. выкидной трубопровод от скважины №887, нефть</t>
-  </si>
-  <si>
-    <t>Сборный нефтегазопровод от куста скважин №54 до т.вр. в сущ. нефтегазосборный трубопровод от ГЗУ-20, нефть</t>
+    <t>ж.ф.+г.ф.</t>
+  </si>
+  <si>
+    <t>Емкость  Е-3</t>
+  </si>
+  <si>
+    <t>Пункт подготовки и сбора нефти высокосернистой «Миннибаевский» с парком резервуарным (НГДУ «Альметьевнефть»)</t>
+  </si>
+  <si>
+    <t>Дегидратор горизонтальный 1ДГ-200</t>
+  </si>
+  <si>
+    <t>Газосепаратор ГСЕ</t>
+  </si>
+  <si>
+    <t>Электродегидратор №4</t>
+  </si>
+  <si>
+    <t>Аппарат 1-200-1.0-1И ТУ26-18-35-89</t>
+  </si>
+  <si>
+    <t>Дегидратор горизонтальный 1ДГ-200 ДГ-1-4</t>
+  </si>
+  <si>
+    <t>Аппарат емкостной ДГ-12 1-200-1-1-Т</t>
+  </si>
+  <si>
+    <t>г.ф.</t>
+  </si>
+  <si>
+    <t>Газопровод внутриплощадочный топливный от ГРПШ до горелок ГП 2,3</t>
+  </si>
+  <si>
+    <t>Газопровод топливный печей ПТБ-10 и ГП</t>
+  </si>
+  <si>
+    <t>Конденсатосборник КС-1</t>
+  </si>
+  <si>
+    <t>Конденсатосборник КС-2</t>
+  </si>
+  <si>
+    <t>Насосное оборудование</t>
+  </si>
+  <si>
+    <t>РВС-5000</t>
+  </si>
+  <si>
+    <t>РВС-4300</t>
+  </si>
+  <si>
+    <t>Трубопровод выхода нефти с КСУ(н)-1,2 до Насосной внешней перекачки</t>
+  </si>
+  <si>
+    <t>Нефтепровод внутриплощадочный от сырьевых насосов до печей ПТБ-10 №3; ГП №2,3</t>
+  </si>
+  <si>
+    <t>Нефтепровод внутриплощадочный дренажный от I до III ступени дегидраторов</t>
+  </si>
+  <si>
+    <t>Внутриплощадочный нефтегазопровод от БЕ до погружной емкости V=80 м³</t>
+  </si>
+  <si>
+    <t>Нефтегазопровод внутриплощадочный от УПС до БСЕ</t>
+  </si>
+  <si>
+    <t>Газопровод внутриплощадочный от УЛФ до УТНГП</t>
+  </si>
+  <si>
+    <t>Газопровод внутриплощадочный от РВС №1,2,3,4 до УЛФ</t>
+  </si>
+  <si>
+    <t>Нефтепровод внутриплощадочный от выкида насосов ЦНС 300×300 №1-3 до узла переключения на ж/д переезде</t>
+  </si>
+  <si>
+    <t>Нефтепровод внутриплощадочный от РВС №1-6 до приема насосов ЦНС 300×300 №1,2,3</t>
   </si>
 </sst>
 </file>
@@ -169,8 +235,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FD86AEF1-A835-43E7-8E63-C1CEC91726C0}" name="Таблица2" displayName="Таблица2" ref="A1:W1048554" totalsRowShown="0">
-  <autoFilter ref="A1:W1048554" xr:uid="{FD86AEF1-A835-43E7-8E63-C1CEC91726C0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FD86AEF1-A835-43E7-8E63-C1CEC91726C0}" name="Таблица2" displayName="Таблица2" ref="A1:W1048552" totalsRowShown="0">
+  <autoFilter ref="A1:W1048552" xr:uid="{FD86AEF1-A835-43E7-8E63-C1CEC91726C0}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{F8505ABD-79CE-4B6A-9D66-BB9AD7197A79}" name="id"/>
     <tableColumn id="2" xr3:uid="{FEC89AEE-6880-4DC1-8494-FD1203EEA743}" name="substance_id"/>
@@ -485,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.33203125" customWidth="1"/>
@@ -585,75 +651,75 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
         <v>26</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="s">
         <v>24</v>
       </c>
       <c r="I2">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="J2">
         <v>89</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Q2">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R2">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="S2">
         <v>3600</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="U2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
@@ -661,151 +727,1562 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
         <v>28</v>
       </c>
       <c r="D3">
-        <v>332</v>
+        <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="s">
         <v>24</v>
       </c>
       <c r="I3">
-        <v>332</v>
+        <v>50</v>
       </c>
       <c r="J3">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N3">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Q3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R3">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="S3">
         <v>3600</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="U3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V3">
         <v>1</v>
       </c>
       <c r="W3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>27</v>
+      <c r="C4" t="s">
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>738</v>
+        <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="s">
         <v>24</v>
       </c>
       <c r="I4">
-        <v>738</v>
+        <v>50</v>
       </c>
       <c r="J4">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="K4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N4">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Q4">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="R4">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="S4">
         <v>3600</v>
       </c>
       <c r="T4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U4">
+        <v>3</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
+      <c r="W4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
         <v>25</v>
       </c>
-      <c r="U4">
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5">
+        <v>50</v>
+      </c>
+      <c r="J5">
+        <v>89</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>190</v>
+      </c>
+      <c r="M5">
+        <v>0.9</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>350</v>
+      </c>
+      <c r="Q5">
+        <v>80</v>
+      </c>
+      <c r="R5">
+        <v>100</v>
+      </c>
+      <c r="S5">
+        <v>3600</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U5">
+        <v>3</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
         <v>4</v>
       </c>
-      <c r="V4">
-        <v>2</v>
-      </c>
-      <c r="W4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="T5" s="1"/>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="T6" s="1"/>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="T7" s="1"/>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6">
+        <v>50</v>
+      </c>
+      <c r="J6">
+        <v>89</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>190</v>
+      </c>
+      <c r="M6">
+        <v>0.9</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>600</v>
+      </c>
+      <c r="Q6">
+        <v>80</v>
+      </c>
+      <c r="R6">
+        <v>100</v>
+      </c>
+      <c r="S6">
+        <v>3600</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U6">
+        <v>3</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7">
+        <v>50</v>
+      </c>
+      <c r="J7">
+        <v>89</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>185</v>
+      </c>
+      <c r="M7">
+        <v>0.9</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>500</v>
+      </c>
+      <c r="Q7">
+        <v>80</v>
+      </c>
+      <c r="R7">
+        <v>100</v>
+      </c>
+      <c r="S7">
+        <v>3600</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U7">
+        <v>3</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+      <c r="W7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8">
+        <v>50</v>
+      </c>
+      <c r="J8">
+        <v>89</v>
+      </c>
+      <c r="K8">
+        <v>3</v>
+      </c>
+      <c r="L8">
+        <v>190</v>
+      </c>
+      <c r="M8">
+        <v>0.9</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>660</v>
+      </c>
+      <c r="Q8">
+        <v>80</v>
+      </c>
+      <c r="R8">
+        <v>100</v>
+      </c>
+      <c r="S8">
+        <v>3600</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U8">
+        <v>3</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9">
+        <v>100</v>
+      </c>
+      <c r="J9">
+        <v>100</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>0.5</v>
+      </c>
+      <c r="O9">
+        <v>20</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>90</v>
+      </c>
+      <c r="R9">
+        <v>5</v>
+      </c>
+      <c r="S9">
+        <v>3600</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U9">
+        <v>3</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="W9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10">
+        <v>369</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10">
+        <v>369</v>
+      </c>
+      <c r="J10">
+        <v>530</v>
+      </c>
+      <c r="K10">
+        <v>3</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1.5</v>
+      </c>
+      <c r="O10">
+        <v>20</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>90</v>
+      </c>
+      <c r="R10">
+        <v>5</v>
+      </c>
+      <c r="S10">
+        <v>3600</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U10">
+        <v>3</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11">
+        <v>50</v>
+      </c>
+      <c r="J11">
+        <v>89</v>
+      </c>
+      <c r="K11">
+        <v>3</v>
+      </c>
+      <c r="L11">
+        <v>30</v>
+      </c>
+      <c r="M11">
+        <v>0.9</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>200</v>
+      </c>
+      <c r="Q11">
+        <v>80</v>
+      </c>
+      <c r="R11">
+        <v>100</v>
+      </c>
+      <c r="S11">
+        <v>3600</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U11">
+        <v>3</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12">
+        <v>50</v>
+      </c>
+      <c r="J12">
+        <v>89</v>
+      </c>
+      <c r="K12">
+        <v>3</v>
+      </c>
+      <c r="L12">
+        <v>60</v>
+      </c>
+      <c r="M12">
+        <v>0.9</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>230</v>
+      </c>
+      <c r="Q12">
+        <v>80</v>
+      </c>
+      <c r="R12">
+        <v>100</v>
+      </c>
+      <c r="S12">
+        <v>3600</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U12">
+        <v>3</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+      <c r="W12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13">
+        <v>27</v>
+      </c>
+      <c r="E13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+      <c r="H13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13">
+        <v>50</v>
+      </c>
+      <c r="J13">
+        <v>100</v>
+      </c>
+      <c r="K13">
+        <v>3</v>
+      </c>
+      <c r="L13">
+        <v>0.2</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>60</v>
+      </c>
+      <c r="Q13">
+        <v>50</v>
+      </c>
+      <c r="R13">
+        <v>100</v>
+      </c>
+      <c r="S13">
+        <v>3600</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U13">
+        <v>3</v>
+      </c>
+      <c r="V13">
+        <v>1</v>
+      </c>
+      <c r="W13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>4</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14">
+        <v>450</v>
+      </c>
+      <c r="J14">
+        <v>159</v>
+      </c>
+      <c r="K14">
+        <v>3</v>
+      </c>
+      <c r="L14">
+        <v>5000</v>
+      </c>
+      <c r="M14">
+        <v>0.9</v>
+      </c>
+      <c r="N14">
+        <v>0.1</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>6000</v>
+      </c>
+      <c r="Q14">
+        <v>60</v>
+      </c>
+      <c r="R14">
+        <v>50</v>
+      </c>
+      <c r="S14">
+        <v>3600</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U14">
+        <v>3</v>
+      </c>
+      <c r="V14">
+        <v>3</v>
+      </c>
+      <c r="W14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15">
+        <v>450</v>
+      </c>
+      <c r="J15">
+        <v>159</v>
+      </c>
+      <c r="K15">
+        <v>3</v>
+      </c>
+      <c r="L15">
+        <v>4300</v>
+      </c>
+      <c r="M15">
+        <v>0.9</v>
+      </c>
+      <c r="N15">
+        <v>0.1</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>3000</v>
+      </c>
+      <c r="Q15">
+        <v>60</v>
+      </c>
+      <c r="R15">
+        <v>50</v>
+      </c>
+      <c r="S15">
+        <v>3600</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U15">
+        <v>3</v>
+      </c>
+      <c r="V15">
+        <v>2</v>
+      </c>
+      <c r="W15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16">
+        <v>171</v>
+      </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16">
+        <v>171</v>
+      </c>
+      <c r="J16">
+        <v>325</v>
+      </c>
+      <c r="K16">
+        <v>5</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>0.16</v>
+      </c>
+      <c r="O16">
+        <v>20</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>90</v>
+      </c>
+      <c r="R16">
+        <v>50</v>
+      </c>
+      <c r="S16">
+        <v>3600</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U16">
+        <v>3</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17">
+        <v>145</v>
+      </c>
+      <c r="E17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17">
+        <v>145</v>
+      </c>
+      <c r="J17">
+        <v>426</v>
+      </c>
+      <c r="K17">
+        <v>5</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>0.16</v>
+      </c>
+      <c r="O17">
+        <v>20</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>90</v>
+      </c>
+      <c r="R17">
+        <v>50</v>
+      </c>
+      <c r="S17">
+        <v>3600</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U17">
+        <v>3</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>4</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18">
+        <v>316</v>
+      </c>
+      <c r="E18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18">
+        <v>316</v>
+      </c>
+      <c r="J18">
+        <v>219</v>
+      </c>
+      <c r="K18">
+        <v>5</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>3.6</v>
+      </c>
+      <c r="O18">
+        <v>20</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>90</v>
+      </c>
+      <c r="R18">
+        <v>50</v>
+      </c>
+      <c r="S18">
+        <v>3600</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U18">
+        <v>3</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19">
+        <v>305</v>
+      </c>
+      <c r="E19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19">
+        <v>305</v>
+      </c>
+      <c r="J19">
+        <v>530</v>
+      </c>
+      <c r="K19">
+        <v>5</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>0.5</v>
+      </c>
+      <c r="O19">
+        <v>20</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>90</v>
+      </c>
+      <c r="R19">
+        <v>50</v>
+      </c>
+      <c r="S19">
+        <v>3600</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U19">
+        <v>3</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20">
+        <v>139</v>
+      </c>
+      <c r="E20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20">
+        <v>139</v>
+      </c>
+      <c r="J20">
+        <v>426</v>
+      </c>
+      <c r="K20">
+        <v>5</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>0.16</v>
+      </c>
+      <c r="O20">
+        <v>20</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>90</v>
+      </c>
+      <c r="R20">
+        <v>50</v>
+      </c>
+      <c r="S20">
+        <v>3600</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U20">
+        <v>3</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>12</v>
+      </c>
+      <c r="B21">
+        <v>6</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21">
+        <v>333</v>
+      </c>
+      <c r="E21" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21">
+        <v>333</v>
+      </c>
+      <c r="J21">
+        <v>219</v>
+      </c>
+      <c r="K21">
+        <v>3</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>0.05</v>
+      </c>
+      <c r="O21">
+        <v>20</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>90</v>
+      </c>
+      <c r="R21">
+        <v>5</v>
+      </c>
+      <c r="S21">
+        <v>3600</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U21">
+        <v>3</v>
+      </c>
+      <c r="V21">
+        <v>1</v>
+      </c>
+      <c r="W21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>13</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22">
+        <v>35</v>
+      </c>
+      <c r="E22" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22">
+        <v>35</v>
+      </c>
+      <c r="J22">
+        <v>219</v>
+      </c>
+      <c r="K22">
+        <v>3</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>0.16</v>
+      </c>
+      <c r="O22">
+        <v>20</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>90</v>
+      </c>
+      <c r="R22">
+        <v>5</v>
+      </c>
+      <c r="S22">
+        <v>3600</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U22">
+        <v>3</v>
+      </c>
+      <c r="V22">
+        <v>1</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>16</v>
+      </c>
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23">
+        <v>1759</v>
+      </c>
+      <c r="E23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23">
+        <v>171</v>
+      </c>
+      <c r="J23">
+        <v>600</v>
+      </c>
+      <c r="K23">
+        <v>5</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>3.3</v>
+      </c>
+      <c r="O23">
+        <v>20</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>90</v>
+      </c>
+      <c r="R23">
+        <v>50</v>
+      </c>
+      <c r="S23">
+        <v>3600</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U23">
+        <v>3</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>17</v>
+      </c>
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24">
+        <v>653</v>
+      </c>
+      <c r="E24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24">
+        <v>103</v>
+      </c>
+      <c r="J24">
+        <v>426</v>
+      </c>
+      <c r="K24">
+        <v>5</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>0.16</v>
+      </c>
+      <c r="O24">
+        <v>20</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>90</v>
+      </c>
+      <c r="R24">
+        <v>50</v>
+      </c>
+      <c r="S24">
+        <v>3600</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U24">
+        <v>3</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
+      </c>
+      <c r="W24">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/equipments/equipment_data.xlsx
+++ b/data/equipments/equipment_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\IRIS_docs\data\equipments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IRIS_docs\data\equipments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC3BB4E-A90B-416C-AC2C-C230E61BDA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93FA0E48-D8A6-498F-B9AC-A495222132D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="192" windowWidth="38916" windowHeight="16488" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="38064" windowHeight="14964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="47">
   <si>
     <t>id</t>
   </si>
@@ -100,89 +100,85 @@
     <t>ж.ф.+г.ф.</t>
   </si>
   <si>
-    <t>Емкость  Е-3</t>
-  </si>
-  <si>
-    <t>Пункт подготовки и сбора нефти высокосернистой «Миннибаевский» с парком резервуарным (НГДУ «Альметьевнефть»)</t>
-  </si>
-  <si>
-    <t>Дегидратор горизонтальный 1ДГ-200</t>
-  </si>
-  <si>
-    <t>Газосепаратор ГСЕ</t>
-  </si>
-  <si>
     <t>Электродегидратор №4</t>
   </si>
   <si>
-    <t>Аппарат 1-200-1.0-1И ТУ26-18-35-89</t>
-  </si>
-  <si>
-    <t>Дегидратор горизонтальный 1ДГ-200 ДГ-1-4</t>
-  </si>
-  <si>
-    <t>Аппарат емкостной ДГ-12 1-200-1-1-Т</t>
-  </si>
-  <si>
     <t>г.ф.</t>
   </si>
   <si>
-    <t>Газопровод внутриплощадочный топливный от ГРПШ до горелок ГП 2,3</t>
-  </si>
-  <si>
-    <t>Газопровод топливный печей ПТБ-10 и ГП</t>
-  </si>
-  <si>
-    <t>Конденсатосборник КС-1</t>
-  </si>
-  <si>
-    <t>Конденсатосборник КС-2</t>
-  </si>
-  <si>
     <t>Насосное оборудование</t>
   </si>
   <si>
-    <t>РВС-5000</t>
-  </si>
-  <si>
-    <t>РВС-4300</t>
-  </si>
-  <si>
-    <t>Трубопровод выхода нефти с КСУ(н)-1,2 до Насосной внешней перекачки</t>
-  </si>
-  <si>
-    <t>Нефтепровод внутриплощадочный от сырьевых насосов до печей ПТБ-10 №3; ГП №2,3</t>
-  </si>
-  <si>
-    <t>Нефтепровод внутриплощадочный дренажный от I до III ступени дегидраторов</t>
-  </si>
-  <si>
-    <t>Внутриплощадочный нефтегазопровод от БЕ до погружной емкости V=80 м³</t>
-  </si>
-  <si>
-    <t>Нефтегазопровод внутриплощадочный от УПС до БСЕ</t>
-  </si>
-  <si>
-    <t>Газопровод внутриплощадочный от УЛФ до УТНГП</t>
-  </si>
-  <si>
-    <t>Газопровод внутриплощадочный от РВС №1,2,3,4 до УЛФ</t>
-  </si>
-  <si>
-    <t>Нефтепровод внутриплощадочный от выкида насосов ЦНС 300×300 №1-3 до узла переключения на ж/д переезде</t>
-  </si>
-  <si>
-    <t>Нефтепровод внутриплощадочный от РВС №1-6 до приема насосов ЦНС 300×300 №1,2,3</t>
+    <t>Концевой делитель фаз КДФ №1, 2</t>
+  </si>
+  <si>
+    <t>Парк резервуарный (промысловый)
+«Миннибаевский» (НГДУ «Альметьевнефть»)</t>
+  </si>
+  <si>
+    <t>Сепаратор №1 -6</t>
+  </si>
+  <si>
+    <t>Емкость дренажная (11 шт.)</t>
+  </si>
+  <si>
+    <t>Внутриплощадочный нефтепровод от РВС №10-18 до нефтенасосной МРП</t>
+  </si>
+  <si>
+    <t>Внутриплощадочный нефтепровод от РВС №23-26 до РВС 20,21 – РВС №16</t>
+  </si>
+  <si>
+    <t>Внутриплощадочный нефтепровод прием РВС №10-18</t>
+  </si>
+  <si>
+    <t>Внутриплощадочный нефтепровод подрезки на РВС №10-18</t>
+  </si>
+  <si>
+    <t>Внутриплощадочный нефтепровод от II ст. сепарации до РВС №23-26</t>
+  </si>
+  <si>
+    <t>Напорный нефтепровод от МТП до ТТП</t>
+  </si>
+  <si>
+    <t>Внутриплощадочный дренажный трубопровод от РВС №20-26 до площ. №1</t>
+  </si>
+  <si>
+    <t>Внутриплощадочный дренажный трубопровод от РВС №10-18 до площ. №2</t>
+  </si>
+  <si>
+    <t>РВС-5000 (Группа резервуаров №№10-18)</t>
+  </si>
+  <si>
+    <t>РВС-5000 (Группа резервуаров №№20-26)</t>
+  </si>
+  <si>
+    <t>РВС-5000 (Группа резервуаров №№1-6)</t>
+  </si>
+  <si>
+    <t>Внутриплощадочный газопровод УЛФ-1,2</t>
+  </si>
+  <si>
+    <t>Компрессор 7ВКГ30/7 №1</t>
+  </si>
+  <si>
+    <t>Внутриплощадочный приемный нефтеводогазопровод II ступени сепарации (выкид с узлов учета до С1-6)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -208,9 +204,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -235,8 +234,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FD86AEF1-A835-43E7-8E63-C1CEC91726C0}" name="Таблица2" displayName="Таблица2" ref="A1:W1048552" totalsRowShown="0">
-  <autoFilter ref="A1:W1048552" xr:uid="{FD86AEF1-A835-43E7-8E63-C1CEC91726C0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FD86AEF1-A835-43E7-8E63-C1CEC91726C0}" name="Таблица2" displayName="Таблица2" ref="A1:W1048546" totalsRowShown="0">
+  <autoFilter ref="A1:W1048546" xr:uid="{FD86AEF1-A835-43E7-8E63-C1CEC91726C0}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{F8505ABD-79CE-4B6A-9D66-BB9AD7197A79}" name="id"/>
     <tableColumn id="2" xr3:uid="{FEC89AEE-6880-4DC1-8494-FD1203EEA743}" name="substance_id"/>
@@ -551,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.33203125" customWidth="1"/>
@@ -651,18 +650,18 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="s">
         <v>25</v>
@@ -686,7 +685,7 @@
         <v>3</v>
       </c>
       <c r="L2">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="M2">
         <v>0.9</v>
@@ -709,8 +708,8 @@
       <c r="S2">
         <v>3600</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>27</v>
+      <c r="T2" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="U2">
         <v>3</v>
@@ -722,15 +721,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -757,7 +756,7 @@
         <v>3</v>
       </c>
       <c r="L3">
-        <v>190</v>
+        <v>32</v>
       </c>
       <c r="M3">
         <v>0.9</v>
@@ -769,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="Q3">
         <v>80</v>
@@ -780,8 +779,8 @@
       <c r="S3">
         <v>3600</v>
       </c>
-      <c r="T3" s="1" t="s">
-        <v>27</v>
+      <c r="T3" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="U3">
         <v>3</v>
@@ -793,15 +792,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -828,7 +827,7 @@
         <v>3</v>
       </c>
       <c r="L4">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="M4">
         <v>0.9</v>
@@ -840,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>350</v>
+        <v>50</v>
       </c>
       <c r="Q4">
         <v>180</v>
@@ -851,31 +850,31 @@
       <c r="S4">
         <v>3600</v>
       </c>
-      <c r="T4" s="1" t="s">
-        <v>27</v>
+      <c r="T4" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="U4">
         <v>3</v>
       </c>
       <c r="V4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
         <v>25</v>
@@ -884,46 +883,46 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="s">
         <v>24</v>
       </c>
       <c r="I5">
-        <v>50</v>
+        <v>450</v>
       </c>
       <c r="J5">
-        <v>89</v>
+        <v>159</v>
       </c>
       <c r="K5">
         <v>3</v>
       </c>
       <c r="L5">
-        <v>190</v>
+        <v>4</v>
       </c>
       <c r="M5">
         <v>0.9</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>350</v>
+        <v>60</v>
       </c>
       <c r="Q5">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="S5">
         <v>3600</v>
       </c>
-      <c r="T5" s="1" t="s">
-        <v>27</v>
+      <c r="T5" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="U5">
         <v>3</v>
@@ -932,21 +931,21 @@
         <v>1</v>
       </c>
       <c r="W5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>1236</v>
       </c>
       <c r="E6" t="s">
         <v>25</v>
@@ -955,69 +954,69 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="s">
         <v>24</v>
       </c>
       <c r="I6">
+        <v>250</v>
+      </c>
+      <c r="J6">
+        <v>325</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>0.16</v>
+      </c>
+      <c r="O6">
+        <v>20</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>90</v>
+      </c>
+      <c r="R6">
         <v>50</v>
-      </c>
-      <c r="J6">
-        <v>89</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>190</v>
-      </c>
-      <c r="M6">
-        <v>0.9</v>
-      </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>600</v>
-      </c>
-      <c r="Q6">
-        <v>80</v>
-      </c>
-      <c r="R6">
-        <v>100</v>
       </c>
       <c r="S6">
         <v>3600</v>
       </c>
-      <c r="T6" s="1" t="s">
-        <v>27</v>
+      <c r="T6" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="U6">
         <v>3</v>
       </c>
       <c r="V6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>145</v>
       </c>
       <c r="E7" t="s">
         <v>25</v>
@@ -1026,69 +1025,69 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="s">
         <v>24</v>
       </c>
       <c r="I7">
+        <v>145</v>
+      </c>
+      <c r="J7">
+        <v>426</v>
+      </c>
+      <c r="K7">
+        <v>5</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>0.16</v>
+      </c>
+      <c r="O7">
+        <v>20</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>90</v>
+      </c>
+      <c r="R7">
         <v>50</v>
-      </c>
-      <c r="J7">
-        <v>89</v>
-      </c>
-      <c r="K7">
-        <v>3</v>
-      </c>
-      <c r="L7">
-        <v>185</v>
-      </c>
-      <c r="M7">
-        <v>0.9</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>500</v>
-      </c>
-      <c r="Q7">
-        <v>80</v>
-      </c>
-      <c r="R7">
-        <v>100</v>
       </c>
       <c r="S7">
         <v>3600</v>
       </c>
-      <c r="T7" s="1" t="s">
-        <v>27</v>
+      <c r="T7" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="U7">
         <v>3</v>
       </c>
       <c r="V7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>316</v>
       </c>
       <c r="E8" t="s">
         <v>25</v>
@@ -1097,72 +1096,72 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="s">
         <v>24</v>
       </c>
       <c r="I8">
+        <v>316</v>
+      </c>
+      <c r="J8">
+        <v>219</v>
+      </c>
+      <c r="K8">
+        <v>5</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>0.7</v>
+      </c>
+      <c r="O8">
+        <v>20</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>90</v>
+      </c>
+      <c r="R8">
         <v>50</v>
-      </c>
-      <c r="J8">
-        <v>89</v>
-      </c>
-      <c r="K8">
-        <v>3</v>
-      </c>
-      <c r="L8">
-        <v>190</v>
-      </c>
-      <c r="M8">
-        <v>0.9</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>660</v>
-      </c>
-      <c r="Q8">
-        <v>80</v>
-      </c>
-      <c r="R8">
-        <v>100</v>
       </c>
       <c r="S8">
         <v>3600</v>
       </c>
-      <c r="T8" s="1" t="s">
-        <v>27</v>
+      <c r="T8" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="U8">
         <v>3</v>
       </c>
       <c r="V8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B9">
-        <v>6</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>35</v>
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
       </c>
       <c r="D9">
-        <v>100</v>
+        <v>412</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1174,13 +1173,13 @@
         <v>24</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>412</v>
       </c>
       <c r="J9">
-        <v>100</v>
+        <v>219</v>
       </c>
       <c r="K9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -1189,7 +1188,7 @@
         <v>1</v>
       </c>
       <c r="N9">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="O9">
         <v>20</v>
@@ -1201,39 +1200,39 @@
         <v>90</v>
       </c>
       <c r="R9">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="S9">
         <v>3600</v>
       </c>
-      <c r="T9" s="1" t="s">
-        <v>27</v>
+      <c r="T9" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="U9">
         <v>3</v>
       </c>
       <c r="V9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B10">
-        <v>6</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>36</v>
+        <v>2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
       </c>
       <c r="D10">
-        <v>369</v>
+        <v>256</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -1245,13 +1244,13 @@
         <v>24</v>
       </c>
       <c r="I10">
-        <v>369</v>
+        <v>256</v>
       </c>
       <c r="J10">
-        <v>530</v>
+        <v>219</v>
       </c>
       <c r="K10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1260,7 +1259,7 @@
         <v>1</v>
       </c>
       <c r="N10">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="O10">
         <v>20</v>
@@ -1272,36 +1271,36 @@
         <v>90</v>
       </c>
       <c r="R10">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="S10">
         <v>3600</v>
       </c>
-      <c r="T10" s="1" t="s">
-        <v>27</v>
+      <c r="T10" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="U10">
         <v>3</v>
       </c>
       <c r="V10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>352</v>
       </c>
       <c r="E11" t="s">
         <v>25</v>
@@ -1310,69 +1309,69 @@
         <v>1</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="s">
         <v>24</v>
       </c>
       <c r="I11">
+        <v>352</v>
+      </c>
+      <c r="J11">
+        <v>219</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>0.7</v>
+      </c>
+      <c r="O11">
+        <v>20</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>90</v>
+      </c>
+      <c r="R11">
         <v>50</v>
-      </c>
-      <c r="J11">
-        <v>89</v>
-      </c>
-      <c r="K11">
-        <v>3</v>
-      </c>
-      <c r="L11">
-        <v>30</v>
-      </c>
-      <c r="M11">
-        <v>0.9</v>
-      </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>200</v>
-      </c>
-      <c r="Q11">
-        <v>80</v>
-      </c>
-      <c r="R11">
-        <v>100</v>
       </c>
       <c r="S11">
         <v>3600</v>
       </c>
-      <c r="T11" s="1" t="s">
-        <v>27</v>
+      <c r="T11" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="U11">
         <v>3</v>
       </c>
       <c r="V11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>220</v>
       </c>
       <c r="E12" t="s">
         <v>25</v>
@@ -1381,66 +1380,66 @@
         <v>1</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="s">
         <v>24</v>
       </c>
       <c r="I12">
+        <v>220</v>
+      </c>
+      <c r="J12">
+        <v>219</v>
+      </c>
+      <c r="K12">
+        <v>5</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>0.7</v>
+      </c>
+      <c r="O12">
+        <v>20</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>90</v>
+      </c>
+      <c r="R12">
         <v>50</v>
-      </c>
-      <c r="J12">
-        <v>89</v>
-      </c>
-      <c r="K12">
-        <v>3</v>
-      </c>
-      <c r="L12">
-        <v>60</v>
-      </c>
-      <c r="M12">
-        <v>0.9</v>
-      </c>
-      <c r="N12">
-        <v>1</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>230</v>
-      </c>
-      <c r="Q12">
-        <v>80</v>
-      </c>
-      <c r="R12">
-        <v>100</v>
       </c>
       <c r="S12">
         <v>3600</v>
       </c>
-      <c r="T12" s="1" t="s">
-        <v>27</v>
+      <c r="T12" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="U12">
         <v>3</v>
       </c>
       <c r="V12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>27</v>
@@ -1490,8 +1489,8 @@
       <c r="S13">
         <v>3600</v>
       </c>
-      <c r="T13" s="1" t="s">
-        <v>27</v>
+      <c r="T13" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="U13">
         <v>3</v>
@@ -1503,18 +1502,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>14</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E14" t="s">
         <v>25</v>
@@ -1538,7 +1537,7 @@
         <v>3</v>
       </c>
       <c r="L14">
-        <v>5000</v>
+        <v>4400</v>
       </c>
       <c r="M14">
         <v>0.9</v>
@@ -1561,8 +1560,8 @@
       <c r="S14">
         <v>3600</v>
       </c>
-      <c r="T14" s="1" t="s">
-        <v>27</v>
+      <c r="T14" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="U14">
         <v>3</v>
@@ -1574,18 +1573,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E15" t="s">
         <v>25</v>
@@ -1609,7 +1608,7 @@
         <v>3</v>
       </c>
       <c r="L15">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="M15">
         <v>0.9</v>
@@ -1621,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>3000</v>
+        <v>6600</v>
       </c>
       <c r="Q15">
         <v>60</v>
@@ -1632,31 +1631,31 @@
       <c r="S15">
         <v>3600</v>
       </c>
-      <c r="T15" s="1" t="s">
-        <v>27</v>
+      <c r="T15" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="U15">
         <v>3</v>
       </c>
       <c r="V15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W15">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16" t="s">
         <v>43</v>
       </c>
       <c r="D16">
-        <v>171</v>
+        <v>6</v>
       </c>
       <c r="E16" t="s">
         <v>25</v>
@@ -1665,37 +1664,37 @@
         <v>1</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="s">
         <v>24</v>
       </c>
       <c r="I16">
-        <v>171</v>
+        <v>450</v>
       </c>
       <c r="J16">
-        <v>325</v>
+        <v>159</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="M16">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N16">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="O16">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="Q16">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="R16">
         <v>50</v>
@@ -1703,34 +1702,34 @@
       <c r="S16">
         <v>3600</v>
       </c>
-      <c r="T16" s="1" t="s">
+      <c r="T16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="U16">
+        <v>3</v>
+      </c>
+      <c r="V16">
+        <v>3</v>
+      </c>
+      <c r="W16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>12</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17">
+        <v>333</v>
+      </c>
+      <c r="E17" t="s">
         <v>27</v>
-      </c>
-      <c r="U16">
-        <v>3</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>17</v>
-      </c>
-      <c r="B17">
-        <v>4</v>
-      </c>
-      <c r="C17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17">
-        <v>145</v>
-      </c>
-      <c r="E17" t="s">
-        <v>25</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1742,13 +1741,13 @@
         <v>24</v>
       </c>
       <c r="I17">
-        <v>145</v>
+        <v>333</v>
       </c>
       <c r="J17">
-        <v>426</v>
+        <v>219</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -1757,7 +1756,7 @@
         <v>1</v>
       </c>
       <c r="N17">
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="O17">
         <v>20</v>
@@ -1769,39 +1768,39 @@
         <v>90</v>
       </c>
       <c r="R17">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="S17">
         <v>3600</v>
       </c>
-      <c r="T17" s="1" t="s">
+      <c r="T17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="U17">
+        <v>3</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+      <c r="W17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>12</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18">
+        <v>120</v>
+      </c>
+      <c r="E18" t="s">
         <v>27</v>
-      </c>
-      <c r="U17">
-        <v>3</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-      <c r="W17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>18</v>
-      </c>
-      <c r="B18">
-        <v>4</v>
-      </c>
-      <c r="C18" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18">
-        <v>316</v>
-      </c>
-      <c r="E18" t="s">
-        <v>25</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -1813,13 +1812,13 @@
         <v>24</v>
       </c>
       <c r="I18">
-        <v>316</v>
+        <v>120</v>
       </c>
       <c r="J18">
-        <v>219</v>
+        <v>120</v>
       </c>
       <c r="K18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -1828,7 +1827,7 @@
         <v>1</v>
       </c>
       <c r="N18">
-        <v>3.6</v>
+        <v>0.1</v>
       </c>
       <c r="O18">
         <v>20</v>
@@ -1840,36 +1839,36 @@
         <v>90</v>
       </c>
       <c r="R18">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="S18">
         <v>3600</v>
       </c>
-      <c r="T18" s="1" t="s">
-        <v>27</v>
+      <c r="T18" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="U18">
         <v>3</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W18">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D19">
-        <v>305</v>
+        <v>230</v>
       </c>
       <c r="E19" t="s">
         <v>25</v>
@@ -1884,10 +1883,10 @@
         <v>24</v>
       </c>
       <c r="I19">
-        <v>305</v>
+        <v>230</v>
       </c>
       <c r="J19">
-        <v>530</v>
+        <v>219</v>
       </c>
       <c r="K19">
         <v>5</v>
@@ -1899,7 +1898,7 @@
         <v>1</v>
       </c>
       <c r="N19">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="O19">
         <v>20</v>
@@ -1916,8 +1915,8 @@
       <c r="S19">
         <v>3600</v>
       </c>
-      <c r="T19" s="1" t="s">
-        <v>27</v>
+      <c r="T19" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="U19">
         <v>3</v>
@@ -1929,18 +1928,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D20">
-        <v>139</v>
+        <v>1920</v>
       </c>
       <c r="E20" t="s">
         <v>25</v>
@@ -1955,10 +1954,10 @@
         <v>24</v>
       </c>
       <c r="I20">
-        <v>139</v>
+        <v>660</v>
       </c>
       <c r="J20">
-        <v>426</v>
+        <v>219</v>
       </c>
       <c r="K20">
         <v>5</v>
@@ -1970,7 +1969,7 @@
         <v>1</v>
       </c>
       <c r="N20">
-        <v>0.16</v>
+        <v>1</v>
       </c>
       <c r="O20">
         <v>20</v>
@@ -1987,8 +1986,8 @@
       <c r="S20">
         <v>3600</v>
       </c>
-      <c r="T20" s="1" t="s">
-        <v>27</v>
+      <c r="T20" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="U20">
         <v>3</v>
@@ -1997,290 +1996,6 @@
         <v>0</v>
       </c>
       <c r="W20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>12</v>
-      </c>
-      <c r="B21">
-        <v>6</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21">
-        <v>333</v>
-      </c>
-      <c r="E21" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I21">
-        <v>333</v>
-      </c>
-      <c r="J21">
-        <v>219</v>
-      </c>
-      <c r="K21">
-        <v>3</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
-      <c r="N21">
-        <v>0.05</v>
-      </c>
-      <c r="O21">
-        <v>20</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>90</v>
-      </c>
-      <c r="R21">
-        <v>5</v>
-      </c>
-      <c r="S21">
-        <v>3600</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="U21">
-        <v>3</v>
-      </c>
-      <c r="V21">
-        <v>1</v>
-      </c>
-      <c r="W21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>13</v>
-      </c>
-      <c r="B22">
-        <v>6</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22">
-        <v>35</v>
-      </c>
-      <c r="E22" t="s">
-        <v>34</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22" t="s">
-        <v>24</v>
-      </c>
-      <c r="I22">
-        <v>35</v>
-      </c>
-      <c r="J22">
-        <v>219</v>
-      </c>
-      <c r="K22">
-        <v>3</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>1</v>
-      </c>
-      <c r="N22">
-        <v>0.16</v>
-      </c>
-      <c r="O22">
-        <v>20</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>90</v>
-      </c>
-      <c r="R22">
-        <v>5</v>
-      </c>
-      <c r="S22">
-        <v>3600</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="U22">
-        <v>3</v>
-      </c>
-      <c r="V22">
-        <v>1</v>
-      </c>
-      <c r="W22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>16</v>
-      </c>
-      <c r="B23">
-        <v>4</v>
-      </c>
-      <c r="C23" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23">
-        <v>1759</v>
-      </c>
-      <c r="E23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23" t="s">
-        <v>24</v>
-      </c>
-      <c r="I23">
-        <v>171</v>
-      </c>
-      <c r="J23">
-        <v>600</v>
-      </c>
-      <c r="K23">
-        <v>5</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>1</v>
-      </c>
-      <c r="N23">
-        <v>3.3</v>
-      </c>
-      <c r="O23">
-        <v>20</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>90</v>
-      </c>
-      <c r="R23">
-        <v>50</v>
-      </c>
-      <c r="S23">
-        <v>3600</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="U23">
-        <v>3</v>
-      </c>
-      <c r="V23">
-        <v>1</v>
-      </c>
-      <c r="W23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>17</v>
-      </c>
-      <c r="B24">
-        <v>4</v>
-      </c>
-      <c r="C24" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24">
-        <v>653</v>
-      </c>
-      <c r="E24" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24" t="s">
-        <v>24</v>
-      </c>
-      <c r="I24">
-        <v>103</v>
-      </c>
-      <c r="J24">
-        <v>426</v>
-      </c>
-      <c r="K24">
-        <v>5</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>1</v>
-      </c>
-      <c r="N24">
-        <v>0.16</v>
-      </c>
-      <c r="O24">
-        <v>20</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
-        <v>90</v>
-      </c>
-      <c r="R24">
-        <v>50</v>
-      </c>
-      <c r="S24">
-        <v>3600</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="U24">
-        <v>3</v>
-      </c>
-      <c r="V24">
-        <v>1</v>
-      </c>
-      <c r="W24">
         <v>2</v>
       </c>
     </row>

--- a/data/equipments/equipment_data.xlsx
+++ b/data/equipments/equipment_data.xlsx
@@ -5,22 +5,35 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IRIS_docs\data\equipments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\IRIS_docs\data\equipments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93FA0E48-D8A6-498F-B9AC-A495222132D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2557D336-4BB7-454C-ACCD-2CCC63160393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="38064" windowHeight="14964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="192" windowWidth="38424" windowHeight="16488" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="44">
   <si>
     <t>id</t>
   </si>
@@ -97,78 +110,68 @@
     <t>[0, 0]</t>
   </si>
   <si>
-    <t>ж.ф.+г.ф.</t>
-  </si>
-  <si>
-    <t>Электродегидратор №4</t>
-  </si>
-  <si>
-    <t>г.ф.</t>
-  </si>
-  <si>
-    <t>Насосное оборудование</t>
-  </si>
-  <si>
-    <t>Концевой делитель фаз КДФ №1, 2</t>
-  </si>
-  <si>
-    <t>Парк резервуарный (промысловый)
-«Миннибаевский» (НГДУ «Альметьевнефть»)</t>
-  </si>
-  <si>
-    <t>Сепаратор №1 -6</t>
-  </si>
-  <si>
-    <t>Емкость дренажная (11 шт.)</t>
-  </si>
-  <si>
-    <t>Внутриплощадочный нефтепровод от РВС №10-18 до нефтенасосной МРП</t>
-  </si>
-  <si>
-    <t>Внутриплощадочный нефтепровод от РВС №23-26 до РВС 20,21 – РВС №16</t>
-  </si>
-  <si>
-    <t>Внутриплощадочный нефтепровод прием РВС №10-18</t>
-  </si>
-  <si>
-    <t>Внутриплощадочный нефтепровод подрезки на РВС №10-18</t>
-  </si>
-  <si>
-    <t>Внутриплощадочный нефтепровод от II ст. сепарации до РВС №23-26</t>
-  </si>
-  <si>
-    <t>Напорный нефтепровод от МТП до ТТП</t>
-  </si>
-  <si>
-    <t>Внутриплощадочный дренажный трубопровод от РВС №20-26 до площ. №1</t>
-  </si>
-  <si>
-    <t>Внутриплощадочный дренажный трубопровод от РВС №10-18 до площ. №2</t>
-  </si>
-  <si>
-    <t>РВС-5000 (Группа резервуаров №№10-18)</t>
-  </si>
-  <si>
-    <t>РВС-5000 (Группа резервуаров №№20-26)</t>
-  </si>
-  <si>
-    <t>РВС-5000 (Группа резервуаров №№1-6)</t>
-  </si>
-  <si>
-    <t>Внутриплощадочный газопровод УЛФ-1,2</t>
-  </si>
-  <si>
-    <t>Компрессор 7ВКГ30/7 №1</t>
-  </si>
-  <si>
-    <t>Внутриплощадочный приемный нефтеводогазопровод II ступени сепарации (выкид с узлов учета до С1-6)</t>
+    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода</t>
+  </si>
+  <si>
+    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от ПК.0 до д. Кувалды, пересечение с а/д, отверстие: "свищ")</t>
+  </si>
+  <si>
+    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от ПК.0 до д. Кувалды, пересечение с а/д, отверстие: "малая трещина")</t>
+  </si>
+  <si>
+    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от ПК.0 до д. Кувалды, пересечение с а/д, отверстие: "средняя трещина")</t>
+  </si>
+  <si>
+    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от ПК.0 до д. Кувалды, пересечение с а/д, отверстие: "гильотинный разрыв")</t>
+  </si>
+  <si>
+    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от д. Кувалды до д. Нов. Мусабай, пересечение с а/д, отверстие: "свищ")</t>
+  </si>
+  <si>
+    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от д. Кувалды до д. Нов. Мусабай, пересечение с а/д, отверстие: "малая трещина")</t>
+  </si>
+  <si>
+    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от д. Кувалды до д. Нов. Мусабай, пересечение с а/д, отверстие: "средняя трещина")</t>
+  </si>
+  <si>
+    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от д. Кувалды до д. Нов. Мусабай, пересечение с а/д, отверстие: "гильотинный разрыв")</t>
+  </si>
+  <si>
+    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от д. Нов. Мусабай до  а/д Альметьевск – Набережные Челны – Нижнекамск , и до ж/д переезда, отверстие: "свищ")</t>
+  </si>
+  <si>
+    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от д. Нов. Мусабай до  а/д Альметьевск – Набережные Челны – Нижнекамск , и до ж/д переезда, отверстие: "малая трещина")</t>
+  </si>
+  <si>
+    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от д. Нов. Мусабай до  а/д Альметьевск – Набережные Челны – Нижнекамск , и до ж/д переезда, отверстие: "средняя трещина")</t>
+  </si>
+  <si>
+    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от д. Нов. Мусабай до  а/д Альметьевск – Набережные Челны – Нижнекамск , и до ж/д переезда, отверстие: "гильотинный разрыв")</t>
+  </si>
+  <si>
+    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от а/д Альметьевск – Набережные Челны – Нижнекамск до ПАО «НКНХ» с пересечением через а/д на д. Биклянь, отверстие: "свищ")</t>
+  </si>
+  <si>
+    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от а/д Альметьевск – Набережные Челны – Нижнекамск до ПАО «НКНХ» с пересечением через а/д на д. Биклянь, отверстие: "малая трещина")</t>
+  </si>
+  <si>
+    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от а/д Альметьевск – Набережные Челны – Нижнекамск до ПАО «НКНХ» с пересечением через а/д на д. Биклянь, отверстие: "средняя трещина")</t>
+  </si>
+  <si>
+    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от а/д Альметьевск – Набережные Челны – Нижнекамск до ПАО «НКНХ» с пересечением через а/д на д. Биклянь, отверстие: "гильотинный разрыв")</t>
+  </si>
+  <si>
+    <t>Насосный агрегат для откачки нефти</t>
+  </si>
+  <si>
+    <t>Камера пуска/приема СОД</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,6 +182,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -204,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -212,6 +222,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -234,8 +245,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FD86AEF1-A835-43E7-8E63-C1CEC91726C0}" name="Таблица2" displayName="Таблица2" ref="A1:W1048546" totalsRowShown="0">
-  <autoFilter ref="A1:W1048546" xr:uid="{FD86AEF1-A835-43E7-8E63-C1CEC91726C0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FD86AEF1-A835-43E7-8E63-C1CEC91726C0}" name="Таблица2" displayName="Таблица2" ref="A1:W1048414" totalsRowShown="0">
+  <autoFilter ref="A1:W1048414" xr:uid="{FD86AEF1-A835-43E7-8E63-C1CEC91726C0}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{F8505ABD-79CE-4B6A-9D66-BB9AD7197A79}" name="id"/>
     <tableColumn id="2" xr3:uid="{FEC89AEE-6880-4DC1-8494-FD1203EEA743}" name="substance_id"/>
@@ -550,12 +561,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.33203125" customWidth="1"/>
     <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="3" width="33.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="19.21875" customWidth="1"/>
     <col min="5" max="5" width="12.77734375" customWidth="1"/>
     <col min="6" max="6" width="12.21875" customWidth="1"/>
@@ -650,211 +661,216 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1489</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2" t="s">
         <v>24</v>
       </c>
       <c r="I2">
-        <v>50</v>
+        <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
+        <v>223.35</v>
       </c>
       <c r="J2">
-        <v>89</v>
+        <v>600</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P2">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R2">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="S2">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="U2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <f>1.28*D2</f>
+        <v>1905.92</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="s">
         <v>24</v>
       </c>
       <c r="I3">
-        <v>50</v>
+        <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
+        <v>285.88799999999998</v>
       </c>
       <c r="J3">
-        <v>89</v>
+        <v>600</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R3">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="S3">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="U3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>32</v>
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <f>1.89*D2</f>
+        <v>2814.21</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="s">
         <v>24</v>
       </c>
       <c r="I4">
-        <v>50</v>
+        <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
+        <v>422.13150000000002</v>
       </c>
       <c r="J4">
-        <v>89</v>
+        <v>600</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P4">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="R4">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="S4">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="U4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V4">
         <v>0</v>
@@ -863,92 +879,94 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <f>2.36*D2</f>
+        <v>3514.04</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
         <v>24</v>
       </c>
       <c r="I5">
-        <v>450</v>
+        <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
+        <v>527.10599999999999</v>
       </c>
       <c r="J5">
-        <v>159</v>
+        <v>600</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N5">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P5">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="R5">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="T5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U5">
+        <v>4</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="U5">
-        <v>3</v>
-      </c>
-      <c r="V5">
-        <v>1</v>
-      </c>
-      <c r="W5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>16</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6">
-        <v>1236</v>
+      <c r="D6" s="3">
+        <v>963</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -960,10 +978,11 @@
         <v>24</v>
       </c>
       <c r="I6">
-        <v>250</v>
+        <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
+        <v>144.44999999999999</v>
       </c>
       <c r="J6">
-        <v>325</v>
+        <v>600</v>
       </c>
       <c r="K6">
         <v>5</v>
@@ -975,7 +994,7 @@
         <v>1</v>
       </c>
       <c r="N6">
-        <v>0.16</v>
+        <v>4</v>
       </c>
       <c r="O6">
         <v>20</v>
@@ -987,39 +1006,40 @@
         <v>90</v>
       </c>
       <c r="R6">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="U6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V6">
         <v>0</v>
       </c>
       <c r="W6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>17</v>
-      </c>
       <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="D7">
-        <v>145</v>
+        <f>1.28*D6</f>
+        <v>1232.6400000000001</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1031,10 +1051,11 @@
         <v>24</v>
       </c>
       <c r="I7">
-        <v>145</v>
+        <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
+        <v>184.89600000000002</v>
       </c>
       <c r="J7">
-        <v>426</v>
+        <v>600</v>
       </c>
       <c r="K7">
         <v>5</v>
@@ -1046,7 +1067,7 @@
         <v>1</v>
       </c>
       <c r="N7">
-        <v>0.16</v>
+        <v>4</v>
       </c>
       <c r="O7">
         <v>20</v>
@@ -1058,39 +1079,40 @@
         <v>90</v>
       </c>
       <c r="R7">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="S7">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="U7">
+        <v>4</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>3</v>
       </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>18</v>
-      </c>
       <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="D8">
-        <v>316</v>
+        <f>1.89*D6</f>
+        <v>1820.07</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1102,10 +1124,11 @@
         <v>24</v>
       </c>
       <c r="I8">
-        <v>316</v>
+        <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
+        <v>273.01049999999998</v>
       </c>
       <c r="J8">
-        <v>219</v>
+        <v>600</v>
       </c>
       <c r="K8">
         <v>5</v>
@@ -1117,7 +1140,7 @@
         <v>1</v>
       </c>
       <c r="N8">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="O8">
         <v>20</v>
@@ -1129,39 +1152,40 @@
         <v>90</v>
       </c>
       <c r="R8">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="S8">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="U8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V8">
         <v>0</v>
       </c>
       <c r="W8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="D9">
-        <v>412</v>
+        <f>2.36*D6</f>
+        <v>2272.6799999999998</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1173,10 +1197,11 @@
         <v>24</v>
       </c>
       <c r="I9">
-        <v>412</v>
+        <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
+        <v>340.90199999999999</v>
       </c>
       <c r="J9">
-        <v>219</v>
+        <v>600</v>
       </c>
       <c r="K9">
         <v>5</v>
@@ -1188,7 +1213,7 @@
         <v>1</v>
       </c>
       <c r="N9">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="O9">
         <v>20</v>
@@ -1200,39 +1225,39 @@
         <v>90</v>
       </c>
       <c r="R9">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="S9">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="U9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10">
-        <v>256</v>
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1698</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -1244,10 +1269,11 @@
         <v>24</v>
       </c>
       <c r="I10">
-        <v>256</v>
+        <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
+        <v>254.7</v>
       </c>
       <c r="J10">
-        <v>219</v>
+        <v>600</v>
       </c>
       <c r="K10">
         <v>5</v>
@@ -1259,7 +1285,7 @@
         <v>1</v>
       </c>
       <c r="N10">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="O10">
         <v>20</v>
@@ -1271,39 +1297,40 @@
         <v>90</v>
       </c>
       <c r="R10">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="S10">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="U10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V10">
         <v>0</v>
       </c>
       <c r="W10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>18</v>
-      </c>
       <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="D11">
-        <v>352</v>
+        <f>1.28*D10</f>
+        <v>2173.44</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1315,10 +1342,11 @@
         <v>24</v>
       </c>
       <c r="I11">
-        <v>352</v>
+        <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
+        <v>326.01600000000002</v>
       </c>
       <c r="J11">
-        <v>219</v>
+        <v>600</v>
       </c>
       <c r="K11">
         <v>5</v>
@@ -1330,7 +1358,7 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="O11">
         <v>20</v>
@@ -1342,39 +1370,40 @@
         <v>90</v>
       </c>
       <c r="R11">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="S11">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="U11">
+        <v>4</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>3</v>
       </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>18</v>
-      </c>
       <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12" t="s">
-        <v>40</v>
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="D12">
-        <v>220</v>
+        <f>1.89*D10</f>
+        <v>3209.22</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1386,10 +1415,11 @@
         <v>24</v>
       </c>
       <c r="I12">
-        <v>220</v>
+        <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
+        <v>481.38299999999992</v>
       </c>
       <c r="J12">
-        <v>219</v>
+        <v>600</v>
       </c>
       <c r="K12">
         <v>5</v>
@@ -1401,7 +1431,7 @@
         <v>1</v>
       </c>
       <c r="N12">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="O12">
         <v>20</v>
@@ -1413,36 +1443,37 @@
         <v>90</v>
       </c>
       <c r="R12">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="S12">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="U12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B13">
-        <v>2</v>
-      </c>
-      <c r="C13" t="s">
-        <v>28</v>
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="D13">
-        <v>27</v>
+        <f>2.36*D10</f>
+        <v>4007.2799999999997</v>
       </c>
       <c r="E13" t="s">
         <v>23</v>
@@ -1451,285 +1482,292 @@
         <v>1</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H13" t="s">
         <v>24</v>
       </c>
       <c r="I13">
-        <v>50</v>
+        <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
+        <v>601.09199999999998</v>
       </c>
       <c r="J13">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="K13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M13">
         <v>1</v>
       </c>
       <c r="N13">
-        <v>7.0000000000000007E-2</v>
+        <v>4</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P13">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="R13">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="S13">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="U13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B14">
-        <v>2</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1100</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="s">
         <v>24</v>
       </c>
       <c r="I14">
-        <v>450</v>
+        <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
+        <v>165</v>
       </c>
       <c r="J14">
-        <v>159</v>
+        <v>600</v>
       </c>
       <c r="K14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>4400</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N14">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P14">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="R14">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="S14">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="U14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>14</v>
-      </c>
       <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <f>1.28*D14</f>
+        <v>1408</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="s">
         <v>24</v>
       </c>
       <c r="I15">
-        <v>450</v>
+        <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
+        <v>211.2</v>
       </c>
       <c r="J15">
-        <v>159</v>
+        <v>600</v>
       </c>
       <c r="K15">
+        <v>5</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>4</v>
+      </c>
+      <c r="O15">
+        <v>20</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>90</v>
+      </c>
+      <c r="R15">
+        <v>5</v>
+      </c>
+      <c r="S15">
+        <v>1800</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U15">
+        <v>4</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>3</v>
       </c>
-      <c r="L15">
-        <v>4400</v>
-      </c>
-      <c r="M15">
-        <v>0.9</v>
-      </c>
-      <c r="N15">
-        <v>0.1</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>6600</v>
-      </c>
-      <c r="Q15">
-        <v>60</v>
-      </c>
-      <c r="R15">
-        <v>50</v>
-      </c>
-      <c r="S15">
-        <v>3600</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U15">
-        <v>3</v>
-      </c>
-      <c r="V15">
-        <v>3</v>
-      </c>
-      <c r="W15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>14</v>
-      </c>
       <c r="B16">
-        <v>2</v>
-      </c>
-      <c r="C16" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <f>1.89*D14</f>
+        <v>2079</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="s">
         <v>24</v>
       </c>
       <c r="I16">
-        <v>450</v>
+        <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
+        <v>311.84999999999997</v>
       </c>
       <c r="J16">
-        <v>159</v>
+        <v>600</v>
       </c>
       <c r="K16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>4400</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N16">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P16">
-        <v>6300</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="R16">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="S16">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="U16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D17">
-        <v>333</v>
+        <f>2.36*D14</f>
+        <v>2596</v>
       </c>
       <c r="E17" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1741,13 +1779,14 @@
         <v>24</v>
       </c>
       <c r="I17">
-        <v>333</v>
+        <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
+        <v>389.4</v>
       </c>
       <c r="J17">
-        <v>219</v>
+        <v>600</v>
       </c>
       <c r="K17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -1756,7 +1795,7 @@
         <v>1</v>
       </c>
       <c r="N17">
-        <v>0.05</v>
+        <v>4</v>
       </c>
       <c r="O17">
         <v>20</v>
@@ -1771,107 +1810,107 @@
         <v>5</v>
       </c>
       <c r="S17">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="U17">
+        <v>4</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+      <c r="W17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>3</v>
       </c>
-      <c r="V17">
-        <v>1</v>
-      </c>
-      <c r="W17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>12</v>
-      </c>
       <c r="B18">
-        <v>3</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>42</v>
       </c>
       <c r="D18">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="E18" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H18" t="s">
         <v>24</v>
       </c>
       <c r="I18">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K18">
         <v>3</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M18">
         <v>1</v>
       </c>
       <c r="N18">
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O18">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Q18">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="R18">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="S18">
         <v>3600</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="U18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B19">
-        <v>2</v>
-      </c>
-      <c r="C19" t="s">
-        <v>46</v>
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="D19">
-        <v>230</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -1883,10 +1922,11 @@
         <v>24</v>
       </c>
       <c r="I19">
-        <v>230</v>
+        <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
+        <v>15</v>
       </c>
       <c r="J19">
-        <v>219</v>
+        <v>600</v>
       </c>
       <c r="K19">
         <v>5</v>
@@ -1898,7 +1938,7 @@
         <v>1</v>
       </c>
       <c r="N19">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="O19">
         <v>20</v>
@@ -1910,93 +1950,22 @@
         <v>90</v>
       </c>
       <c r="R19">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="S19">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="U19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="B20">
-        <v>2</v>
-      </c>
-      <c r="C20" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20">
-        <v>1920</v>
-      </c>
-      <c r="E20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20" t="s">
-        <v>24</v>
-      </c>
-      <c r="I20">
-        <v>660</v>
-      </c>
-      <c r="J20">
-        <v>219</v>
-      </c>
-      <c r="K20">
-        <v>5</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-      <c r="N20">
-        <v>1</v>
-      </c>
-      <c r="O20">
-        <v>20</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>90</v>
-      </c>
-      <c r="R20">
-        <v>50</v>
-      </c>
-      <c r="S20">
-        <v>3600</v>
-      </c>
-      <c r="T20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U20">
-        <v>3</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/equipments/equipment_data.xlsx
+++ b/data/equipments/equipment_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\IRIS_docs\data\equipments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2557D336-4BB7-454C-ACCD-2CCC63160393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA8E560-B95E-4BFA-95AF-7AFE715369D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="192" windowWidth="38424" windowHeight="16488" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2856" yWindow="192" windowWidth="38424" windowHeight="16488" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment Data" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="47">
   <si>
     <t>id</t>
   </si>
@@ -110,61 +110,70 @@
     <t>[0, 0]</t>
   </si>
   <si>
-    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода</t>
-  </si>
-  <si>
-    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от ПК.0 до д. Кувалды, пересечение с а/д, отверстие: "свищ")</t>
-  </si>
-  <si>
-    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от ПК.0 до д. Кувалды, пересечение с а/д, отверстие: "малая трещина")</t>
-  </si>
-  <si>
-    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от ПК.0 до д. Кувалды, пересечение с а/д, отверстие: "средняя трещина")</t>
-  </si>
-  <si>
-    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от ПК.0 до д. Кувалды, пересечение с а/д, отверстие: "гильотинный разрыв")</t>
-  </si>
-  <si>
-    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от д. Кувалды до д. Нов. Мусабай, пересечение с а/д, отверстие: "свищ")</t>
-  </si>
-  <si>
-    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от д. Кувалды до д. Нов. Мусабай, пересечение с а/д, отверстие: "малая трещина")</t>
-  </si>
-  <si>
-    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от д. Кувалды до д. Нов. Мусабай, пересечение с а/д, отверстие: "средняя трещина")</t>
-  </si>
-  <si>
-    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от д. Кувалды до д. Нов. Мусабай, пересечение с а/д, отверстие: "гильотинный разрыв")</t>
-  </si>
-  <si>
-    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от д. Нов. Мусабай до  а/д Альметьевск – Набережные Челны – Нижнекамск , и до ж/д переезда, отверстие: "свищ")</t>
-  </si>
-  <si>
-    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от д. Нов. Мусабай до  а/д Альметьевск – Набережные Челны – Нижнекамск , и до ж/д переезда, отверстие: "малая трещина")</t>
-  </si>
-  <si>
-    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от д. Нов. Мусабай до  а/д Альметьевск – Набережные Челны – Нижнекамск , и до ж/д переезда, отверстие: "средняя трещина")</t>
-  </si>
-  <si>
-    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от д. Нов. Мусабай до  а/д Альметьевск – Набережные Челны – Нижнекамск , и до ж/д переезда, отверстие: "гильотинный разрыв")</t>
-  </si>
-  <si>
-    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от а/д Альметьевск – Набережные Челны – Нижнекамск до ПАО «НКНХ» с пересечением через а/д на д. Биклянь, отверстие: "свищ")</t>
-  </si>
-  <si>
-    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от а/д Альметьевск – Набережные Челны – Нижнекамск до ПАО «НКНХ» с пересечением через а/д на д. Биклянь, отверстие: "малая трещина")</t>
-  </si>
-  <si>
-    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от а/д Альметьевск – Набережные Челны – Нижнекамск до ПАО «НКНХ» с пересечением через а/д на д. Биклянь, отверстие: "средняя трещина")</t>
-  </si>
-  <si>
-    <t>Участок магистрального нефтепровода Нефтеперерабатывающего завода (от а/д Альметьевск – Набережные Челны – Нижнекамск до ПАО «НКНХ» с пересечением через а/д на д. Биклянь, отверстие: "гильотинный разрыв")</t>
-  </si>
-  <si>
-    <t>Насосный агрегат для откачки нефти</t>
-  </si>
-  <si>
     <t>Камера пуска/приема СОД</t>
+  </si>
+  <si>
+    <t>Участок магистрального продуктопровода НПЗ ОАО «ТАИФ-НК»</t>
+  </si>
+  <si>
+    <t>Участок магистрального продуктопровода НПЗ ОАО «ТАИФ-НК» (уч-к на территории ОАО «ТАИФ-НК» и ПАО «Нижнекамскнефтехим», отверстие: "свищ")</t>
+  </si>
+  <si>
+    <t>Участок магистрального продуктопровода НПЗ ОАО «ТАИФ-НК» (уч-к на территории ОАО «ТАИФ-НК» и ПАО «Нижнекамскнефтехим», отверстие: "малая трещина")</t>
+  </si>
+  <si>
+    <t>Участок магистрального продуктопровода НПЗ ОАО «ТАИФ-НК» (уч-к на территории ОАО «ТАИФ-НК» и ПАО «Нижнекамскнефтехим», отверстие: "средняя трещина")</t>
+  </si>
+  <si>
+    <t>Участок магистрального продуктопровода НПЗ ОАО «ТАИФ-НК» (уч-к на территории ОАО «ТАИФ-НК» и ПАО «Нижнекамскнефтехим», отверстие: "гильотинный разрыв")</t>
+  </si>
+  <si>
+    <t>Участок магистрального продуктопровода НПЗ ОАО «ТАИФ-НК» (уч-к 1340 м от ТП, пересечение с а/д, отверстие: "свищ")</t>
+  </si>
+  <si>
+    <t>Участок магистрального продуктопровода НПЗ ОАО «ТАИФ-НК» (уч-к 1340 м от ТПй, пересечение с а/д, отверстие: "малая трещина")</t>
+  </si>
+  <si>
+    <t>Участок магистрального продуктопровода НПЗ ОАО «ТАИФ-НК» (уч-к 1340 м от ТП, пересечение с а/д, отверстие: "средняя трещина")</t>
+  </si>
+  <si>
+    <t>Участок магистрального продуктопровода НПЗ ОАО «ТАИФ-НК» (уч-к 1340 м от ТП, пересечение с а/д, отверстие: "гильотинный разрыв")</t>
+  </si>
+  <si>
+    <t>Участок магистрального продуктопровода НПЗ ОАО «ТАИФ-НК» (уч-к 1250 м от начала ТП, пересечение с ж/д, отверстие: "свищ")</t>
+  </si>
+  <si>
+    <t>Участок магистрального продуктопровода НПЗ ОАО «ТАИФ-НК» (уч-к 1250 м от начала ТП, пересечение с ж/да, отверстие: "малая трещина")</t>
+  </si>
+  <si>
+    <t>Участок магистрального продуктопровода НПЗ ОАО «ТАИФ-НК» (уч-к 1250 м от начала ТП, пересечение с ж/д, отверстие: "средняя трещина")</t>
+  </si>
+  <si>
+    <t>Участок магистрального продуктопровода НПЗ ОАО «ТАИФ-НК» (уч-к 1250 м от начала ТП, пересечение с ж/д, отверстие: "гильотинный разрыв")</t>
+  </si>
+  <si>
+    <t>Участок магистрального продуктопровода НПЗ ОАО «ТАИФ-НК» (уч-к 1900 м от начала ТП, пересечение с ж/д, отверстие: "свищ")</t>
+  </si>
+  <si>
+    <t>Участок магистрального продуктопровода НПЗ ОАО «ТАИФ-НК» (уч-к 1900 м от начала ТП, пересечение с ж/д, отверстие: "средняя трещина")</t>
+  </si>
+  <si>
+    <t>Участок магистрального продуктопровода НПЗ ОАО «ТАИФ-НК» (уч-к 1900 м от начала ТП, пересечение с ж/д, отверстие: "гильотинный разрыв")</t>
+  </si>
+  <si>
+    <t>Насосный агрегат для перекачивания ДТ</t>
+  </si>
+  <si>
+    <t>Участок магистрального продуктопровода НПЗ ОАО «ТАИФ-НК» (уч-к 2230 м от начала ТП, пересечение с водн.преградой, отверстие: "свищ")</t>
+  </si>
+  <si>
+    <t>Участок магистрального продуктопровода НПЗ ОАО «ТАИФ-НК» (уч-к 2230 м от начала ТП, пересечение с водн.преградой, отверстие: "малая трещина")</t>
+  </si>
+  <si>
+    <t>Участок магистрального продуктопровода НПЗ ОАО «ТАИФ-НК» (уч-к 2230 м от начала ТП, пересечение с водн.преградой, отверстие: "средняя трещина")</t>
+  </si>
+  <si>
+    <t>Участок магистрального продуктопровода НПЗ ОАО «ТАИФ-НК» (уч-к 2230 м от начала ТП, пересечение с водн.преградой, отверстие: "гильотинный разрыв")</t>
   </si>
 </sst>
 </file>
@@ -561,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.33203125" customWidth="1"/>
@@ -661,7 +670,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -669,10 +678,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="3">
-        <v>1489</v>
+        <v>909</v>
       </c>
       <c r="E2" t="s">
         <v>23</v>
@@ -688,7 +697,7 @@
       </c>
       <c r="I2">
         <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
-        <v>223.35</v>
+        <v>136.35</v>
       </c>
       <c r="J2">
         <v>600</v>
@@ -721,7 +730,7 @@
         <v>1800</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U2">
         <v>4</v>
@@ -733,7 +742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -741,11 +750,11 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <f>1.28*D2</f>
-        <v>1905.92</v>
+        <v>1163.52</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
@@ -761,7 +770,7 @@
       </c>
       <c r="I3">
         <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
-        <v>285.88799999999998</v>
+        <v>174.52799999999999</v>
       </c>
       <c r="J3">
         <v>600</v>
@@ -794,7 +803,7 @@
         <v>1800</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U3">
         <v>4</v>
@@ -806,7 +815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -814,11 +823,11 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <f>1.89*D2</f>
-        <v>2814.21</v>
+        <v>1718.01</v>
       </c>
       <c r="E4" t="s">
         <v>23</v>
@@ -834,7 +843,7 @@
       </c>
       <c r="I4">
         <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
-        <v>422.13150000000002</v>
+        <v>257.70150000000001</v>
       </c>
       <c r="J4">
         <v>600</v>
@@ -867,7 +876,7 @@
         <v>1800</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U4">
         <v>4</v>
@@ -879,7 +888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -887,11 +896,11 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5">
         <f>2.36*D2</f>
-        <v>3514.04</v>
+        <v>2145.2399999999998</v>
       </c>
       <c r="E5" t="s">
         <v>23</v>
@@ -907,7 +916,7 @@
       </c>
       <c r="I5">
         <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
-        <v>527.10599999999999</v>
+        <v>321.78599999999994</v>
       </c>
       <c r="J5">
         <v>600</v>
@@ -940,7 +949,7 @@
         <v>1800</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U5">
         <v>4</v>
@@ -952,7 +961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -960,10 +969,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" s="3">
-        <v>963</v>
+        <v>1206</v>
       </c>
       <c r="E6" t="s">
         <v>23</v>
@@ -979,7 +988,7 @@
       </c>
       <c r="I6">
         <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
-        <v>144.44999999999999</v>
+        <v>180.9</v>
       </c>
       <c r="J6">
         <v>600</v>
@@ -1012,7 +1021,7 @@
         <v>1800</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U6">
         <v>4</v>
@@ -1032,11 +1041,11 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7">
         <f>1.28*D6</f>
-        <v>1232.6400000000001</v>
+        <v>1543.68</v>
       </c>
       <c r="E7" t="s">
         <v>23</v>
@@ -1052,7 +1061,7 @@
       </c>
       <c r="I7">
         <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
-        <v>184.89600000000002</v>
+        <v>231.55199999999999</v>
       </c>
       <c r="J7">
         <v>600</v>
@@ -1085,7 +1094,7 @@
         <v>1800</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U7">
         <v>4</v>
@@ -1105,11 +1114,11 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8">
         <f>1.89*D6</f>
-        <v>1820.07</v>
+        <v>2279.3399999999997</v>
       </c>
       <c r="E8" t="s">
         <v>23</v>
@@ -1125,7 +1134,7 @@
       </c>
       <c r="I8">
         <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
-        <v>273.01049999999998</v>
+        <v>341.90099999999995</v>
       </c>
       <c r="J8">
         <v>600</v>
@@ -1158,7 +1167,7 @@
         <v>1800</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U8">
         <v>4</v>
@@ -1178,11 +1187,11 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9">
         <f>2.36*D6</f>
-        <v>2272.6799999999998</v>
+        <v>2846.16</v>
       </c>
       <c r="E9" t="s">
         <v>23</v>
@@ -1198,7 +1207,7 @@
       </c>
       <c r="I9">
         <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
-        <v>340.90199999999999</v>
+        <v>426.92399999999998</v>
       </c>
       <c r="J9">
         <v>600</v>
@@ -1231,7 +1240,7 @@
         <v>1800</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U9">
         <v>4</v>
@@ -1243,7 +1252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1251,10 +1260,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" s="3">
-        <v>1698</v>
+        <v>1250</v>
       </c>
       <c r="E10" t="s">
         <v>23</v>
@@ -1270,7 +1279,7 @@
       </c>
       <c r="I10">
         <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
-        <v>254.7</v>
+        <v>187.5</v>
       </c>
       <c r="J10">
         <v>600</v>
@@ -1303,7 +1312,7 @@
         <v>1800</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U10">
         <v>4</v>
@@ -1315,7 +1324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1323,11 +1332,11 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D11">
         <f>1.28*D10</f>
-        <v>2173.44</v>
+        <v>1600</v>
       </c>
       <c r="E11" t="s">
         <v>23</v>
@@ -1343,7 +1352,7 @@
       </c>
       <c r="I11">
         <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
-        <v>326.01600000000002</v>
+        <v>240</v>
       </c>
       <c r="J11">
         <v>600</v>
@@ -1376,7 +1385,7 @@
         <v>1800</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U11">
         <v>4</v>
@@ -1388,7 +1397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>3</v>
       </c>
@@ -1396,11 +1405,11 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D12">
         <f>1.89*D10</f>
-        <v>3209.22</v>
+        <v>2362.5</v>
       </c>
       <c r="E12" t="s">
         <v>23</v>
@@ -1416,7 +1425,7 @@
       </c>
       <c r="I12">
         <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
-        <v>481.38299999999992</v>
+        <v>354.375</v>
       </c>
       <c r="J12">
         <v>600</v>
@@ -1449,7 +1458,7 @@
         <v>1800</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U12">
         <v>4</v>
@@ -1461,7 +1470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>4</v>
       </c>
@@ -1469,11 +1478,11 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13">
         <f>2.36*D10</f>
-        <v>4007.2799999999997</v>
+        <v>2950</v>
       </c>
       <c r="E13" t="s">
         <v>23</v>
@@ -1489,7 +1498,7 @@
       </c>
       <c r="I13">
         <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
-        <v>601.09199999999998</v>
+        <v>442.5</v>
       </c>
       <c r="J13">
         <v>600</v>
@@ -1522,19 +1531,19 @@
         <v>1800</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U13">
         <v>4</v>
       </c>
       <c r="V13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1</v>
       </c>
@@ -1542,10 +1551,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="3">
-        <v>1100</v>
+        <v>1450</v>
       </c>
       <c r="E14" t="s">
         <v>23</v>
@@ -1561,7 +1570,7 @@
       </c>
       <c r="I14">
         <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
-        <v>165</v>
+        <v>217.5</v>
       </c>
       <c r="J14">
         <v>600</v>
@@ -1594,7 +1603,7 @@
         <v>1800</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U14">
         <v>4</v>
@@ -1606,7 +1615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1614,11 +1623,11 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D15">
         <f>1.28*D14</f>
-        <v>1408</v>
+        <v>1856</v>
       </c>
       <c r="E15" t="s">
         <v>23</v>
@@ -1634,7 +1643,7 @@
       </c>
       <c r="I15">
         <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
-        <v>211.2</v>
+        <v>278.39999999999998</v>
       </c>
       <c r="J15">
         <v>600</v>
@@ -1667,7 +1676,7 @@
         <v>1800</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U15">
         <v>4</v>
@@ -1679,7 +1688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>3</v>
       </c>
@@ -1691,7 +1700,7 @@
       </c>
       <c r="D16">
         <f>1.89*D14</f>
-        <v>2079</v>
+        <v>2740.5</v>
       </c>
       <c r="E16" t="s">
         <v>23</v>
@@ -1707,7 +1716,7 @@
       </c>
       <c r="I16">
         <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
-        <v>311.84999999999997</v>
+        <v>411.07499999999999</v>
       </c>
       <c r="J16">
         <v>600</v>
@@ -1740,7 +1749,7 @@
         <v>1800</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U16">
         <v>4</v>
@@ -1752,7 +1761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>4</v>
       </c>
@@ -1764,7 +1773,7 @@
       </c>
       <c r="D17">
         <f>2.36*D14</f>
-        <v>2596</v>
+        <v>3422</v>
       </c>
       <c r="E17" t="s">
         <v>23</v>
@@ -1780,7 +1789,7 @@
       </c>
       <c r="I17">
         <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
-        <v>389.4</v>
+        <v>513.29999999999995</v>
       </c>
       <c r="J17">
         <v>600</v>
@@ -1813,30 +1822,30 @@
         <v>1800</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U17">
         <v>4</v>
       </c>
       <c r="V17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
-      <c r="C18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18">
-        <v>10</v>
+      <c r="C18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="3">
+        <v>803</v>
       </c>
       <c r="E18" t="s">
         <v>23</v>
@@ -1845,46 +1854,47 @@
         <v>1</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H18" t="s">
         <v>24</v>
       </c>
       <c r="I18">
-        <v>50</v>
+        <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
+        <v>120.44999999999999</v>
       </c>
       <c r="J18">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="K18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M18">
         <v>1</v>
       </c>
       <c r="N18">
-        <v>7.0000000000000007E-2</v>
+        <v>4</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="S18">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U18">
         <v>4</v>
@@ -1896,18 +1906,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D19">
-        <v>100</v>
+        <f>1.28*D18</f>
+        <v>1027.8399999999999</v>
       </c>
       <c r="E19" t="s">
         <v>23</v>
@@ -1923,7 +1934,7 @@
       </c>
       <c r="I19">
         <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
-        <v>15</v>
+        <v>154.17599999999999</v>
       </c>
       <c r="J19">
         <v>600</v>
@@ -1941,7 +1952,7 @@
         <v>4</v>
       </c>
       <c r="O19">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -1956,15 +1967,304 @@
         <v>1800</v>
       </c>
       <c r="T19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="U19">
+        <v>4</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20">
+        <f>1.89*D18</f>
+        <v>1517.6699999999998</v>
+      </c>
+      <c r="E20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20">
+        <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
+        <v>227.65049999999997</v>
+      </c>
+      <c r="J20">
+        <v>600</v>
+      </c>
+      <c r="K20">
+        <v>5</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>4</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>90</v>
+      </c>
+      <c r="R20">
+        <v>5</v>
+      </c>
+      <c r="S20">
+        <v>1800</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="U20">
+        <v>4</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>4</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21">
+        <f>2.36*D18</f>
+        <v>1895.08</v>
+      </c>
+      <c r="E21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21">
+        <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
+        <v>284.262</v>
+      </c>
+      <c r="J21">
+        <v>600</v>
+      </c>
+      <c r="K21">
+        <v>5</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>4</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>90</v>
+      </c>
+      <c r="R21">
+        <v>5</v>
+      </c>
+      <c r="S21">
+        <v>1800</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="U21">
+        <v>4</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22">
+        <v>10</v>
+      </c>
+      <c r="E22" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22">
+        <v>50</v>
+      </c>
+      <c r="J22">
+        <v>100</v>
+      </c>
+      <c r="K22">
+        <v>3</v>
+      </c>
+      <c r="L22">
+        <v>0.2</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>70</v>
+      </c>
+      <c r="Q22">
+        <v>50</v>
+      </c>
+      <c r="R22">
+        <v>100</v>
+      </c>
+      <c r="S22">
+        <v>3600</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="U22">
+        <v>4</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>4</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="U19">
-        <v>4</v>
-      </c>
-      <c r="V19">
-        <v>1</v>
-      </c>
-      <c r="W19">
+      <c r="D23">
+        <v>140</v>
+      </c>
+      <c r="E23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23">
+        <f>Таблица2[[#This Row],[quantity_equipment]]*0.15</f>
+        <v>21</v>
+      </c>
+      <c r="J23">
+        <v>600</v>
+      </c>
+      <c r="K23">
+        <v>5</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>4</v>
+      </c>
+      <c r="O23">
+        <v>20</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>90</v>
+      </c>
+      <c r="R23">
+        <v>5</v>
+      </c>
+      <c r="S23">
+        <v>1800</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="U23">
+        <v>4</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23">
         <v>1</v>
       </c>
     </row>
